--- a/planilha_transferencias_audesp.xlsx
+++ b/planilha_transferencias_audesp.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="63">
   <si>
     <t>FICHA</t>
   </si>
@@ -29,6 +29,12 @@
   </si>
   <si>
     <t>VALOR</t>
+  </si>
+  <si>
+    <t>COD_APLICACAO_PARCEIRO</t>
+  </si>
+  <si>
+    <t>VALOR_TOTAL_NEGATIVO</t>
   </si>
   <si>
     <t>HISTORICO_CUSTOM</t>
@@ -554,10 +560,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H65"/>
+  <dimension ref="A1:J65"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -582,1285 +588,1675 @@
       <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:8">
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E2">
         <v>45.54</v>
       </c>
-      <c r="G2" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
+      <c r="F2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G2">
+        <v>45.54</v>
+      </c>
+      <c r="I2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E3">
         <v>45.54</v>
       </c>
-      <c r="G3" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
+      <c r="F3" t="s">
+        <v>32</v>
+      </c>
+      <c r="G3">
+        <v>45.54</v>
+      </c>
+      <c r="I3" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C4" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D4" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E4">
         <v>938.17</v>
       </c>
-      <c r="G4" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
+      <c r="F4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G4">
+        <v>938.17</v>
+      </c>
+      <c r="I4" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D5" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E5">
         <v>938.17</v>
       </c>
-      <c r="G5" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
+      <c r="F5" t="s">
+        <v>33</v>
+      </c>
+      <c r="G5">
+        <v>938.17</v>
+      </c>
+      <c r="I5" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C6" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E6">
         <v>70429.23</v>
       </c>
-      <c r="G6" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
+      <c r="F6" t="s">
+        <v>33</v>
+      </c>
+      <c r="G6">
+        <v>93832.32000000001</v>
+      </c>
+      <c r="I6" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D7" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E7">
         <v>70429.23</v>
       </c>
-      <c r="G7" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
+      <c r="F7" t="s">
+        <v>34</v>
+      </c>
+      <c r="G7">
+        <v>93832.32000000001</v>
+      </c>
+      <c r="I7" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D8" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E8">
         <v>251.42</v>
       </c>
-      <c r="G8" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8">
+      <c r="F8" t="s">
+        <v>35</v>
+      </c>
+      <c r="G8">
+        <v>93832.32000000001</v>
+      </c>
+      <c r="I8" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
       <c r="A9" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D9" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E9">
         <v>251.42</v>
       </c>
-      <c r="G9" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8">
+      <c r="F9" t="s">
+        <v>34</v>
+      </c>
+      <c r="G9">
+        <v>93832.32000000001</v>
+      </c>
+      <c r="I9" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
       <c r="A10" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C10" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D10" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E10">
         <v>23151.67</v>
       </c>
-      <c r="G10" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8">
+      <c r="F10" t="s">
+        <v>36</v>
+      </c>
+      <c r="G10">
+        <v>93832.32000000001</v>
+      </c>
+      <c r="I10" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
       <c r="A11" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C11" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D11" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E11">
         <v>23151.67</v>
       </c>
-      <c r="G11" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8">
+      <c r="F11" t="s">
+        <v>34</v>
+      </c>
+      <c r="G11">
+        <v>93832.32000000001</v>
+      </c>
+      <c r="I11" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
       <c r="A12" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C12" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D12" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E12">
         <v>77631.55</v>
       </c>
-      <c r="G12" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8">
+      <c r="F12" t="s">
+        <v>36</v>
+      </c>
+      <c r="G12">
+        <v>77631.55</v>
+      </c>
+      <c r="I12" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
       <c r="A13" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C13" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E13">
         <v>77631.55</v>
       </c>
-      <c r="G13" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8">
+      <c r="F13" t="s">
+        <v>35</v>
+      </c>
+      <c r="G13">
+        <v>77631.55</v>
+      </c>
+      <c r="I13" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
       <c r="A14" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C14" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D14" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E14">
         <v>9697.799999999999</v>
       </c>
-      <c r="G14" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8">
+      <c r="F14" t="s">
+        <v>36</v>
+      </c>
+      <c r="G14">
+        <v>9697.799999999999</v>
+      </c>
+      <c r="I14" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
       <c r="A15" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B15" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C15" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D15" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E15">
         <v>9697.799999999999</v>
       </c>
-      <c r="G15" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8">
+      <c r="F15" t="s">
+        <v>37</v>
+      </c>
+      <c r="G15">
+        <v>9697.799999999999</v>
+      </c>
+      <c r="I15" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
       <c r="A16" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B16" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C16" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D16" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E16">
         <v>5063.53</v>
       </c>
-      <c r="G16" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
+      <c r="F16" t="s">
+        <v>38</v>
+      </c>
+      <c r="G16">
+        <v>5063.53</v>
+      </c>
+      <c r="I16" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
       <c r="A17" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B17" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C17" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D17" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E17">
         <v>5063.53</v>
       </c>
-      <c r="G17" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
+      <c r="F17" t="s">
+        <v>33</v>
+      </c>
+      <c r="G17">
+        <v>5063.53</v>
+      </c>
+      <c r="I17" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
       <c r="A18" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B18" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C18" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D18" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E18">
         <v>1446.48</v>
       </c>
-      <c r="G18" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
+      <c r="F18" t="s">
+        <v>33</v>
+      </c>
+      <c r="G18">
+        <v>1446.48</v>
+      </c>
+      <c r="I18" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
       <c r="A19" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B19" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C19" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D19" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E19">
         <v>1446.48</v>
       </c>
-      <c r="G19" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
+      <c r="F19" t="s">
+        <v>39</v>
+      </c>
+      <c r="G19">
+        <v>1446.48</v>
+      </c>
+      <c r="I19" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
       <c r="A20" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B20" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C20" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D20" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E20">
         <v>18952.13</v>
       </c>
-      <c r="G20" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
+      <c r="F20" t="s">
+        <v>38</v>
+      </c>
+      <c r="G20">
+        <v>18952.13</v>
+      </c>
+      <c r="I20" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
       <c r="A21" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B21" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C21" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D21" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E21">
         <v>18952.13</v>
       </c>
-      <c r="G21" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
+      <c r="F21" t="s">
+        <v>33</v>
+      </c>
+      <c r="G21">
+        <v>18952.13</v>
+      </c>
+      <c r="I21" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
       <c r="A22" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B22" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C22" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D22" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E22">
         <v>4403.17</v>
       </c>
-      <c r="G22" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
+      <c r="F22" t="s">
+        <v>41</v>
+      </c>
+      <c r="G22">
+        <v>4403.17</v>
+      </c>
+      <c r="I22" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9">
       <c r="A23" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B23" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C23" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D23" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E23">
         <v>4403.17</v>
       </c>
-      <c r="G23" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
+      <c r="F23" t="s">
+        <v>40</v>
+      </c>
+      <c r="G23">
+        <v>4403.17</v>
+      </c>
+      <c r="I23" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9">
       <c r="A24" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B24" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C24" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D24" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E24">
         <v>17031.81</v>
       </c>
-      <c r="G24" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
+      <c r="F24" t="s">
+        <v>38</v>
+      </c>
+      <c r="G24">
+        <v>17031.81</v>
+      </c>
+      <c r="I24" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9">
       <c r="A25" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B25" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C25" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D25" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E25">
         <v>17031.81</v>
       </c>
-      <c r="G25" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
+      <c r="F25" t="s">
+        <v>33</v>
+      </c>
+      <c r="G25">
+        <v>17031.81</v>
+      </c>
+      <c r="I25" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9">
       <c r="A26" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B26" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C26" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D26" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E26">
         <v>1663.2</v>
       </c>
-      <c r="G26" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
+      <c r="F26" t="s">
+        <v>43</v>
+      </c>
+      <c r="G26">
+        <v>1663.2</v>
+      </c>
+      <c r="I26" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9">
       <c r="A27" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B27" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C27" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D27" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E27">
         <v>1663.2</v>
       </c>
-      <c r="G27" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
+      <c r="F27" t="s">
+        <v>42</v>
+      </c>
+      <c r="G27">
+        <v>1663.2</v>
+      </c>
+      <c r="I27" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9">
       <c r="A28" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B28" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C28" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D28" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E28">
         <v>123821.82</v>
       </c>
-      <c r="G28" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
+      <c r="F28" t="s">
+        <v>43</v>
+      </c>
+      <c r="G28">
+        <v>123821.82</v>
+      </c>
+      <c r="I28" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9">
       <c r="A29" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B29" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C29" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D29" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E29">
         <v>123821.82</v>
       </c>
-      <c r="G29" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
+      <c r="F29" t="s">
+        <v>44</v>
+      </c>
+      <c r="G29">
+        <v>123821.82</v>
+      </c>
+      <c r="I29" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9">
       <c r="A30" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B30" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C30" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D30" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E30">
         <v>1461234.24</v>
       </c>
-      <c r="G30" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7">
+      <c r="F30" t="s">
+        <v>46</v>
+      </c>
+      <c r="G30">
+        <v>1461234.24</v>
+      </c>
+      <c r="I30" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9">
       <c r="A31" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B31" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C31" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D31" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E31">
         <v>1461234.24</v>
       </c>
-      <c r="G31" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7">
+      <c r="F31" t="s">
+        <v>45</v>
+      </c>
+      <c r="G31">
+        <v>1461234.24</v>
+      </c>
+      <c r="I31" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9">
       <c r="A32" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B32" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C32" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D32" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E32">
         <v>551292.54</v>
       </c>
-      <c r="G32" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7">
+      <c r="F32" t="s">
+        <v>46</v>
+      </c>
+      <c r="G32">
+        <v>551292.54</v>
+      </c>
+      <c r="I32" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9">
       <c r="A33" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B33" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C33" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D33" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E33">
         <v>551292.54</v>
       </c>
-      <c r="G33" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7">
+      <c r="F33" t="s">
+        <v>47</v>
+      </c>
+      <c r="G33">
+        <v>551292.54</v>
+      </c>
+      <c r="I33" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9">
       <c r="A34" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B34" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C34" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D34" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E34">
         <v>734450.49</v>
       </c>
-      <c r="G34" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7">
+      <c r="F34" t="s">
+        <v>46</v>
+      </c>
+      <c r="G34">
+        <v>734450.49</v>
+      </c>
+      <c r="I34" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9">
       <c r="A35" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B35" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C35" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D35" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E35">
         <v>734450.49</v>
       </c>
-      <c r="G35" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7">
+      <c r="F35" t="s">
+        <v>48</v>
+      </c>
+      <c r="G35">
+        <v>734450.49</v>
+      </c>
+      <c r="I35" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9">
       <c r="A36" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B36" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C36" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D36" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E36">
         <v>265786.66</v>
       </c>
-      <c r="G36" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7">
+      <c r="F36" t="s">
+        <v>46</v>
+      </c>
+      <c r="G36">
+        <v>265786.66</v>
+      </c>
+      <c r="I36" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9">
       <c r="A37" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B37" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C37" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D37" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E37">
         <v>265786.66</v>
       </c>
-      <c r="G37" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7">
+      <c r="F37" t="s">
+        <v>49</v>
+      </c>
+      <c r="G37">
+        <v>265786.66</v>
+      </c>
+      <c r="I37" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9">
       <c r="A38" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B38" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C38" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D38" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E38">
         <v>30382.2</v>
       </c>
-      <c r="G38" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7">
+      <c r="F38" t="s">
+        <v>46</v>
+      </c>
+      <c r="G38">
+        <v>30382.2</v>
+      </c>
+      <c r="I38" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9">
       <c r="A39" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B39" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C39" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D39" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E39">
         <v>30382.2</v>
       </c>
-      <c r="G39" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7">
+      <c r="F39" t="s">
+        <v>50</v>
+      </c>
+      <c r="G39">
+        <v>30382.2</v>
+      </c>
+      <c r="I39" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9">
       <c r="A40" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B40" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C40" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D40" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E40">
         <v>3858.64</v>
       </c>
-      <c r="G40" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7">
+      <c r="F40" t="s">
+        <v>52</v>
+      </c>
+      <c r="G40">
+        <v>5664.64</v>
+      </c>
+      <c r="I40" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9">
       <c r="A41" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B41" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C41" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D41" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E41">
         <v>3858.64</v>
       </c>
-      <c r="G41" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7">
+      <c r="F41" t="s">
+        <v>51</v>
+      </c>
+      <c r="G41">
+        <v>5664.64</v>
+      </c>
+      <c r="I41" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9">
       <c r="A42" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B42" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C42" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D42" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E42">
         <v>5000.8</v>
       </c>
-      <c r="G42" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7">
+      <c r="F42" t="s">
+        <v>43</v>
+      </c>
+      <c r="G42">
+        <v>5000.8</v>
+      </c>
+      <c r="I42" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9">
       <c r="A43" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B43" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C43" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D43" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E43">
         <v>5000.8</v>
       </c>
-      <c r="G43" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7">
+      <c r="F43" t="s">
+        <v>53</v>
+      </c>
+      <c r="G43">
+        <v>5000.8</v>
+      </c>
+      <c r="I43" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9">
       <c r="A44" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B44" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C44" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D44" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E44">
         <v>97.42</v>
       </c>
-      <c r="G44" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7">
+      <c r="F44" t="s">
+        <v>33</v>
+      </c>
+      <c r="G44">
+        <v>116.4</v>
+      </c>
+      <c r="I44" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9">
       <c r="A45" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B45" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C45" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D45" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E45">
         <v>97.42</v>
       </c>
-      <c r="G45" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7">
+      <c r="F45" t="s">
+        <v>54</v>
+      </c>
+      <c r="G45">
+        <v>116.4</v>
+      </c>
+      <c r="I45" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9">
       <c r="A46" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B46" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C46" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D46" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E46">
         <v>18.98</v>
       </c>
-      <c r="G46" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7">
+      <c r="F46" t="s">
+        <v>55</v>
+      </c>
+      <c r="G46">
+        <v>116.4</v>
+      </c>
+      <c r="I46" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9">
       <c r="A47" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B47" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C47" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D47" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E47">
         <v>18.98</v>
       </c>
-      <c r="G47" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7">
+      <c r="F47" t="s">
+        <v>54</v>
+      </c>
+      <c r="G47">
+        <v>116.4</v>
+      </c>
+      <c r="I47" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9">
       <c r="A48" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B48" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C48" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D48" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E48">
         <v>38501.38</v>
       </c>
-      <c r="G48" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7">
+      <c r="F48" t="s">
+        <v>55</v>
+      </c>
+      <c r="G48">
+        <v>105637.59</v>
+      </c>
+      <c r="I48" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9">
       <c r="A49" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B49" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C49" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D49" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E49">
         <v>38501.38</v>
       </c>
-      <c r="G49" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7">
+      <c r="F49" t="s">
+        <v>56</v>
+      </c>
+      <c r="G49">
+        <v>105637.59</v>
+      </c>
+      <c r="I49" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9">
       <c r="A50" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B50" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C50" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D50" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E50">
         <v>67136.21000000001</v>
       </c>
-      <c r="G50" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7">
+      <c r="F50" t="s">
+        <v>57</v>
+      </c>
+      <c r="G50">
+        <v>105637.59</v>
+      </c>
+      <c r="I50" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9">
       <c r="A51" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B51" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C51" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D51" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E51">
         <v>67136.21000000001</v>
       </c>
-      <c r="G51" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7">
+      <c r="F51" t="s">
+        <v>56</v>
+      </c>
+      <c r="G51">
+        <v>105637.59</v>
+      </c>
+      <c r="I51" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9">
       <c r="A52" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B52" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C52" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D52" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E52">
         <v>78461.92</v>
       </c>
-      <c r="G52" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7">
+      <c r="F52" t="s">
+        <v>57</v>
+      </c>
+      <c r="G52">
+        <v>78461.92</v>
+      </c>
+      <c r="I52" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9">
       <c r="A53" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B53" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C53" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D53" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E53">
         <v>78461.92</v>
       </c>
-      <c r="G53" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7">
+      <c r="F53" t="s">
+        <v>58</v>
+      </c>
+      <c r="G53">
+        <v>78461.92</v>
+      </c>
+      <c r="I53" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9">
       <c r="A54" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B54" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C54" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D54" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E54">
         <v>8287.23</v>
       </c>
-      <c r="G54" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7">
+      <c r="F54" t="s">
+        <v>41</v>
+      </c>
+      <c r="G54">
+        <v>8287.23</v>
+      </c>
+      <c r="I54" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9">
       <c r="A55" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B55" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C55" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D55" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E55">
         <v>8287.23</v>
       </c>
-      <c r="G55" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7">
+      <c r="F55" t="s">
+        <v>59</v>
+      </c>
+      <c r="G55">
+        <v>8287.23</v>
+      </c>
+      <c r="I55" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9">
       <c r="A56" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B56" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C56" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D56" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E56">
         <v>1149.04</v>
       </c>
-      <c r="G56" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7">
+      <c r="F56" t="s">
+        <v>38</v>
+      </c>
+      <c r="G56">
+        <v>1149.04</v>
+      </c>
+      <c r="I56" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9">
       <c r="A57" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B57" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C57" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D57" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E57">
         <v>1149.04</v>
       </c>
-      <c r="G57" t="s">
+      <c r="F57" t="s">
+        <v>33</v>
+      </c>
+      <c r="G57">
+        <v>1149.04</v>
+      </c>
+      <c r="I57" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9">
+      <c r="A58" t="s">
+        <v>24</v>
+      </c>
+      <c r="B58" t="s">
+        <v>27</v>
+      </c>
+      <c r="C58" t="s">
+        <v>30</v>
+      </c>
+      <c r="D58" t="s">
         <v>60</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7">
-      <c r="A58" t="s">
-        <v>22</v>
-      </c>
-      <c r="B58" t="s">
-        <v>25</v>
-      </c>
-      <c r="C58" t="s">
-        <v>28</v>
-      </c>
-      <c r="D58" t="s">
-        <v>58</v>
       </c>
       <c r="E58">
         <v>64401.82</v>
       </c>
-      <c r="G58" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7">
+      <c r="F58" t="s">
+        <v>33</v>
+      </c>
+      <c r="G58">
+        <v>64401.82</v>
+      </c>
+      <c r="I58" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9">
       <c r="A59" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B59" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C59" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D59" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E59">
         <v>64401.82</v>
       </c>
-      <c r="G59" t="s">
+      <c r="F59" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="60" spans="1:7">
+      <c r="G59">
+        <v>64401.82</v>
+      </c>
+      <c r="I59" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9">
       <c r="A60" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B60" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C60" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D60" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E60">
         <v>160118.05</v>
       </c>
-      <c r="G60" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7">
+      <c r="F60" t="s">
+        <v>33</v>
+      </c>
+      <c r="G60">
+        <v>160118.05</v>
+      </c>
+      <c r="I60" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9">
       <c r="A61" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B61" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C61" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D61" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E61">
         <v>160118.05</v>
       </c>
-      <c r="G61" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7">
+      <c r="F61" t="s">
+        <v>61</v>
+      </c>
+      <c r="G61">
+        <v>160118.05</v>
+      </c>
+      <c r="I61" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9">
       <c r="A62" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B62" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C62" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D62" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E62">
         <v>135.08</v>
       </c>
-      <c r="G62" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7">
+      <c r="F62" t="s">
+        <v>32</v>
+      </c>
+      <c r="G62">
+        <v>135.08</v>
+      </c>
+      <c r="I62" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9">
       <c r="A63" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B63" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C63" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D63" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E63">
         <v>135.08</v>
       </c>
-      <c r="G63" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7">
+      <c r="F63" t="s">
+        <v>32</v>
+      </c>
+      <c r="G63">
+        <v>135.08</v>
+      </c>
+      <c r="I63" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9">
       <c r="A64" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B64" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C64" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D64" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E64">
         <v>897.88</v>
       </c>
-      <c r="G64" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7">
+      <c r="F64" t="s">
+        <v>33</v>
+      </c>
+      <c r="G64">
+        <v>897.88</v>
+      </c>
+      <c r="I64" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9">
       <c r="A65" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B65" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C65" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D65" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E65">
         <v>897.88</v>
       </c>
-      <c r="G65" t="s">
-        <v>60</v>
+      <c r="F65" t="s">
+        <v>33</v>
+      </c>
+      <c r="G65">
+        <v>897.88</v>
+      </c>
+      <c r="I65" t="s">
+        <v>62</v>
       </c>
     </row>
   </sheetData>

--- a/planilha_transferencias_audesp.xlsx
+++ b/planilha_transferencias_audesp.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="526" uniqueCount="69">
   <si>
     <t>FICHA</t>
   </si>
@@ -70,6 +70,9 @@
     <t>1421</t>
   </si>
   <si>
+    <t>1438</t>
+  </si>
+  <si>
     <t>1442</t>
   </si>
   <si>
@@ -91,6 +94,12 @@
     <t>1498</t>
   </si>
   <si>
+    <t>1514</t>
+  </si>
+  <si>
+    <t>1515</t>
+  </si>
+  <si>
     <t>1516</t>
   </si>
   <si>
@@ -139,67 +148,76 @@
     <t>801.0006 - Emenda N° 202508766173 - Dp. Sebastião Santos</t>
   </si>
   <si>
+    <t>300.0000 - SAÚDE</t>
+  </si>
+  <si>
+    <t>801.0002 - Emenda N° 202532272366 - Dp. André Bueno</t>
+  </si>
+  <si>
+    <t>801.0011 - Emenda Parlamentar n° 202532268852 - Dp. André Bueno</t>
+  </si>
+  <si>
+    <t>261.0000 - EDUCAÇÃO - FUNDEB - MAGISTÉRIO / Profissionais da Educação</t>
+  </si>
+  <si>
+    <t>260.0000 - EDUCAÇÃO - FUNDEB</t>
+  </si>
+  <si>
+    <t>262.0000 - EDUCAÇÃO - FUNDEB - OUTROS</t>
+  </si>
+  <si>
+    <t>271.0000 - EDUCAÇÃO - FUNDEB - MAGISTÉRIO / Profissionais da Educação - CRECHE</t>
+  </si>
+  <si>
+    <t>272.0000 - EDUCAÇÃO - FUNDEB - MAGISTÉRIO / Profissionais da Educação - PRÉ-ESCOLA</t>
+  </si>
+  <si>
+    <t>273.0000 - EDUCAÇÃO - FUNDEB - OUTROS - CRECHE</t>
+  </si>
+  <si>
+    <t>500.0000 - ASSISTÊNCIA SOCIAL</t>
+  </si>
+  <si>
+    <t>511.0000 - REMUNERAÇÃO DE APLICAÇÕES FINANCEIRAS</t>
+  </si>
+  <si>
+    <t>302.0000 - ATENÇÃO DE MÉDIA E ALTA COMPLEXIDADE AMBULATORIAL E HOSPITALAR</t>
+  </si>
+  <si>
+    <t>280.0000 - GERAL</t>
+  </si>
+  <si>
+    <t>280.0000 - RECURSOS DO SALÁRIO EDUCAÇÃO - CRECHE</t>
+  </si>
+  <si>
+    <t>221.0000 - REMUNERAÇÃO DE APLICAÇÕES FINANCEIRAS</t>
+  </si>
+  <si>
+    <t>282.0000 - RECURSOS DO SALÁRIO EDUCAÇÃO - ENSINO FUNDAMENTAL</t>
+  </si>
+  <si>
+    <t>281.0000 - RECURSOS DO SALÁRIO EDUCAÇÃO - PRÉ-ESCOLA</t>
+  </si>
+  <si>
+    <t>301.0000 - ATENÇÃO BÁSICA</t>
+  </si>
+  <si>
     <t>311.0000 - REMUNERAÇÃO DE APLICAÇÕES FINANCEIRAS</t>
   </si>
   <si>
-    <t>801.0002 - Emenda N° 202532272366 - Dp. André Bueno</t>
-  </si>
-  <si>
-    <t>300.0000 - SAÚDE</t>
-  </si>
-  <si>
-    <t>801.0011 - Emenda Parlamentar n° 202532268852 - Dp. André Bueno</t>
-  </si>
-  <si>
-    <t>261.0000 - EDUCAÇÃO - FUNDEB - MAGISTÉRIO / Profissionais da Educação</t>
-  </si>
-  <si>
-    <t>260.0000 - EDUCAÇÃO - FUNDEB</t>
-  </si>
-  <si>
-    <t>262.0000 - EDUCAÇÃO - FUNDEB - OUTROS</t>
-  </si>
-  <si>
-    <t>271.0000 - EDUCAÇÃO - FUNDEB - MAGISTÉRIO / Profissionais da Educação - CRECHE</t>
-  </si>
-  <si>
-    <t>272.0000 - EDUCAÇÃO - FUNDEB - MAGISTÉRIO / Profissionais da Educação - PRÉ-ESCOLA</t>
-  </si>
-  <si>
-    <t>273.0000 - EDUCAÇÃO - FUNDEB - OUTROS - CRECHE</t>
-  </si>
-  <si>
-    <t>500.0000 - ASSISTÊNCIA SOCIAL</t>
-  </si>
-  <si>
-    <t>511.0000 - REMUNERAÇÃO DE APLICAÇÕES FINANCEIRAS</t>
-  </si>
-  <si>
-    <t>302.0000 - ATENÇÃO DE MÉDIA E ALTA COMPLEXIDADE AMBULATORIAL E HOSPITALAR</t>
-  </si>
-  <si>
-    <t>280.0000 - GERAL</t>
-  </si>
-  <si>
-    <t>221.0000 - REMUNERAÇÃO DE APLICAÇÕES FINANCEIRAS</t>
-  </si>
-  <si>
-    <t>280.0000 - RECURSOS DO SALÁRIO EDUCAÇÃO - CRECHE</t>
-  </si>
-  <si>
-    <t>282.0000 - RECURSOS DO SALÁRIO EDUCAÇÃO - ENSINO FUNDAMENTAL</t>
-  </si>
-  <si>
-    <t>281.0000 - RECURSOS DO SALÁRIO EDUCAÇÃO - PRÉ-ESCOLA</t>
-  </si>
-  <si>
-    <t>301.0000 - ATENÇÃO BÁSICA</t>
-  </si>
-  <si>
     <t>410.0000 - TRÂNSITO - SINALIZAÇÃO</t>
   </si>
   <si>
     <t>510.0000 - ASSISTÊNCIA SOCIAL - GERAL</t>
+  </si>
+  <si>
+    <t>800.0010 - Emenda N° 1574159700012500000 - Dp. Vicentinho</t>
+  </si>
+  <si>
+    <t>800.0004 - Emenda N° 157415970001/25-010 - Dp. Marcos Pereira</t>
+  </si>
+  <si>
+    <t>800.0005 - Emenda N° 36000654021202500 - Dp. Jonas Donizete</t>
   </si>
   <si>
     <t>PENDENTE</t>
@@ -560,7 +578,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J65"/>
+  <dimension ref="A1:J87"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:10">
@@ -600,25 +618,25 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D2" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E2">
         <v>45.54</v>
       </c>
       <c r="F2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="G2">
         <v>45.54</v>
       </c>
       <c r="I2" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -626,25 +644,25 @@
         <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C3" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D3" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E3">
         <v>45.54</v>
       </c>
       <c r="F3" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G3">
         <v>45.54</v>
       </c>
       <c r="I3" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -652,25 +670,25 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C4" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D4" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E4">
         <v>938.17</v>
       </c>
       <c r="F4" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="G4">
         <v>938.17</v>
       </c>
       <c r="I4" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -678,25 +696,25 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C5" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D5" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E5">
         <v>938.17</v>
       </c>
       <c r="F5" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="G5">
         <v>938.17</v>
       </c>
       <c r="I5" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -704,25 +722,25 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C6" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D6" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E6">
         <v>70429.23</v>
       </c>
       <c r="F6" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="G6">
         <v>93832.32000000001</v>
       </c>
       <c r="I6" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -730,25 +748,25 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C7" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D7" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E7">
         <v>70429.23</v>
       </c>
       <c r="F7" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G7">
         <v>93832.32000000001</v>
       </c>
       <c r="I7" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -756,25 +774,25 @@
         <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C8" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D8" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E8">
         <v>251.42</v>
       </c>
       <c r="F8" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G8">
         <v>93832.32000000001</v>
       </c>
       <c r="I8" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -782,25 +800,25 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C9" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D9" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E9">
         <v>251.42</v>
       </c>
       <c r="F9" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G9">
         <v>93832.32000000001</v>
       </c>
       <c r="I9" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -808,25 +826,25 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C10" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D10" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E10">
         <v>23151.67</v>
       </c>
       <c r="F10" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G10">
         <v>93832.32000000001</v>
       </c>
       <c r="I10" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -834,25 +852,25 @@
         <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C11" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D11" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E11">
         <v>23151.67</v>
       </c>
       <c r="F11" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G11">
         <v>93832.32000000001</v>
       </c>
       <c r="I11" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -860,25 +878,25 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C12" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D12" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E12">
         <v>77631.55</v>
       </c>
       <c r="F12" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G12">
         <v>77631.55</v>
       </c>
       <c r="I12" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -886,25 +904,25 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C13" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D13" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E13">
         <v>77631.55</v>
       </c>
       <c r="F13" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G13">
         <v>77631.55</v>
       </c>
       <c r="I13" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -912,25 +930,25 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C14" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D14" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E14">
         <v>9697.799999999999</v>
       </c>
       <c r="F14" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G14">
         <v>9697.799999999999</v>
       </c>
       <c r="I14" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -938,25 +956,25 @@
         <v>11</v>
       </c>
       <c r="B15" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C15" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D15" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E15">
         <v>9697.799999999999</v>
       </c>
       <c r="F15" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G15">
         <v>9697.799999999999</v>
       </c>
       <c r="I15" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -964,25 +982,25 @@
         <v>12</v>
       </c>
       <c r="B16" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C16" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D16" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E16">
         <v>5063.53</v>
       </c>
       <c r="F16" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G16">
         <v>5063.53</v>
       </c>
       <c r="I16" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
     </row>
     <row r="17" spans="1:9">
@@ -990,25 +1008,25 @@
         <v>12</v>
       </c>
       <c r="B17" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C17" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D17" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="E17">
         <v>5063.53</v>
       </c>
       <c r="F17" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="G17">
         <v>5063.53</v>
       </c>
       <c r="I17" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
     </row>
     <row r="18" spans="1:9">
@@ -1016,25 +1034,25 @@
         <v>13</v>
       </c>
       <c r="B18" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C18" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D18" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E18">
         <v>1446.48</v>
       </c>
       <c r="F18" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="G18">
         <v>1446.48</v>
       </c>
       <c r="I18" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
     </row>
     <row r="19" spans="1:9">
@@ -1042,25 +1060,25 @@
         <v>13</v>
       </c>
       <c r="B19" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C19" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D19" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E19">
         <v>1446.48</v>
       </c>
       <c r="F19" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="G19">
         <v>1446.48</v>
       </c>
       <c r="I19" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
     </row>
     <row r="20" spans="1:9">
@@ -1068,25 +1086,25 @@
         <v>14</v>
       </c>
       <c r="B20" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C20" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D20" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E20">
         <v>18952.13</v>
       </c>
       <c r="F20" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G20">
         <v>18952.13</v>
       </c>
       <c r="I20" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
     </row>
     <row r="21" spans="1:9">
@@ -1094,25 +1112,25 @@
         <v>14</v>
       </c>
       <c r="B21" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C21" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D21" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="E21">
         <v>18952.13</v>
       </c>
       <c r="F21" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="G21">
         <v>18952.13</v>
       </c>
       <c r="I21" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
     </row>
     <row r="22" spans="1:9">
@@ -1120,25 +1138,25 @@
         <v>15</v>
       </c>
       <c r="B22" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C22" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D22" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="E22">
-        <v>4403.17</v>
+        <v>3566.46</v>
       </c>
       <c r="F22" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="G22">
         <v>4403.17</v>
       </c>
       <c r="I22" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
     </row>
     <row r="23" spans="1:9">
@@ -1146,129 +1164,129 @@
         <v>15</v>
       </c>
       <c r="B23" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C23" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D23" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="E23">
-        <v>4403.17</v>
+        <v>3566.46</v>
       </c>
       <c r="F23" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G23">
         <v>4403.17</v>
       </c>
       <c r="I23" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
     </row>
     <row r="24" spans="1:9">
       <c r="A24" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B24" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C24" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D24" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="E24">
-        <v>17031.81</v>
+        <v>836.71</v>
       </c>
       <c r="F24" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="G24">
-        <v>17031.81</v>
+        <v>4403.17</v>
       </c>
       <c r="I24" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
     </row>
     <row r="25" spans="1:9">
       <c r="A25" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B25" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C25" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D25" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="E25">
-        <v>17031.81</v>
+        <v>836.71</v>
       </c>
       <c r="F25" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="G25">
-        <v>17031.81</v>
+        <v>4403.17</v>
       </c>
       <c r="I25" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
     </row>
     <row r="26" spans="1:9">
       <c r="A26" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B26" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C26" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D26" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E26">
-        <v>1663.2</v>
+        <v>17031.81</v>
       </c>
       <c r="F26" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G26">
-        <v>1663.2</v>
+        <v>17031.81</v>
       </c>
       <c r="I26" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
     </row>
     <row r="27" spans="1:9">
       <c r="A27" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B27" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C27" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D27" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E27">
-        <v>1663.2</v>
+        <v>17031.81</v>
       </c>
       <c r="F27" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="G27">
-        <v>1663.2</v>
+        <v>17031.81</v>
       </c>
       <c r="I27" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
     </row>
     <row r="28" spans="1:9">
@@ -1276,25 +1294,25 @@
         <v>17</v>
       </c>
       <c r="B28" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C28" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D28" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E28">
-        <v>123821.82</v>
+        <v>1663.2</v>
       </c>
       <c r="F28" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="G28">
-        <v>123821.82</v>
+        <v>1663.2</v>
       </c>
       <c r="I28" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
     </row>
     <row r="29" spans="1:9">
@@ -1302,129 +1320,129 @@
         <v>17</v>
       </c>
       <c r="B29" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C29" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D29" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="E29">
-        <v>123821.82</v>
+        <v>1663.2</v>
       </c>
       <c r="F29" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G29">
-        <v>123821.82</v>
+        <v>1663.2</v>
       </c>
       <c r="I29" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
     </row>
     <row r="30" spans="1:9">
       <c r="A30" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B30" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C30" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D30" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E30">
-        <v>1461234.24</v>
+        <v>325.67</v>
       </c>
       <c r="F30" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="G30">
-        <v>1461234.24</v>
+        <v>123821.82</v>
       </c>
       <c r="I30" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
     </row>
     <row r="31" spans="1:9">
       <c r="A31" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B31" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C31" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D31" t="s">
+        <v>36</v>
+      </c>
+      <c r="E31">
+        <v>325.67</v>
+      </c>
+      <c r="F31" t="s">
         <v>46</v>
       </c>
-      <c r="E31">
-        <v>1461234.24</v>
-      </c>
-      <c r="F31" t="s">
-        <v>45</v>
-      </c>
       <c r="G31">
-        <v>1461234.24</v>
+        <v>123821.82</v>
       </c>
       <c r="I31" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
     </row>
     <row r="32" spans="1:9">
       <c r="A32" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B32" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C32" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D32" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E32">
-        <v>551292.54</v>
+        <v>123496.15</v>
       </c>
       <c r="F32" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G32">
-        <v>551292.54</v>
+        <v>123821.82</v>
       </c>
       <c r="I32" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
     </row>
     <row r="33" spans="1:9">
       <c r="A33" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B33" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C33" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D33" t="s">
+        <v>44</v>
+      </c>
+      <c r="E33">
+        <v>123496.15</v>
+      </c>
+      <c r="F33" t="s">
         <v>46</v>
       </c>
-      <c r="E33">
-        <v>551292.54</v>
-      </c>
-      <c r="F33" t="s">
-        <v>47</v>
-      </c>
       <c r="G33">
-        <v>551292.54</v>
+        <v>123821.82</v>
       </c>
       <c r="I33" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
     </row>
     <row r="34" spans="1:9">
@@ -1432,25 +1450,25 @@
         <v>18</v>
       </c>
       <c r="B34" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C34" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D34" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="E34">
-        <v>734450.49</v>
+        <v>108347.67</v>
       </c>
       <c r="F34" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="G34">
-        <v>734450.49</v>
+        <v>108347.67</v>
       </c>
       <c r="I34" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
     </row>
     <row r="35" spans="1:9">
@@ -1458,129 +1476,129 @@
         <v>18</v>
       </c>
       <c r="B35" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C35" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D35" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="E35">
-        <v>734450.49</v>
+        <v>108347.67</v>
       </c>
       <c r="F35" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="G35">
-        <v>734450.49</v>
+        <v>108347.67</v>
       </c>
       <c r="I35" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
     </row>
     <row r="36" spans="1:9">
       <c r="A36" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B36" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C36" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D36" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E36">
-        <v>265786.66</v>
+        <v>742117.09</v>
       </c>
       <c r="F36" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="G36">
-        <v>265786.66</v>
+        <v>1461234.24</v>
       </c>
       <c r="I36" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
     </row>
     <row r="37" spans="1:9">
       <c r="A37" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B37" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C37" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D37" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="E37">
-        <v>265786.66</v>
+        <v>742117.09</v>
       </c>
       <c r="F37" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="G37">
-        <v>265786.66</v>
+        <v>1461234.24</v>
       </c>
       <c r="I37" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
     </row>
     <row r="38" spans="1:9">
       <c r="A38" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B38" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C38" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D38" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E38">
-        <v>30382.2</v>
+        <v>719117.15</v>
       </c>
       <c r="F38" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G38">
-        <v>30382.2</v>
+        <v>1461234.24</v>
       </c>
       <c r="I38" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
     </row>
     <row r="39" spans="1:9">
       <c r="A39" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B39" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C39" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D39" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E39">
-        <v>30382.2</v>
+        <v>719117.15</v>
       </c>
       <c r="F39" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="G39">
-        <v>30382.2</v>
+        <v>1461234.24</v>
       </c>
       <c r="I39" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
     </row>
     <row r="40" spans="1:9">
@@ -1588,25 +1606,25 @@
         <v>19</v>
       </c>
       <c r="B40" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C40" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D40" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E40">
-        <v>3858.64</v>
+        <v>551292.54</v>
       </c>
       <c r="F40" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G40">
-        <v>5664.64</v>
+        <v>551292.54</v>
       </c>
       <c r="I40" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
     </row>
     <row r="41" spans="1:9">
@@ -1614,285 +1632,285 @@
         <v>19</v>
       </c>
       <c r="B41" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C41" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D41" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="E41">
-        <v>3858.64</v>
+        <v>551292.54</v>
       </c>
       <c r="F41" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G41">
-        <v>5664.64</v>
+        <v>551292.54</v>
       </c>
       <c r="I41" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
     </row>
     <row r="42" spans="1:9">
       <c r="A42" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B42" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C42" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D42" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="E42">
-        <v>5000.8</v>
+        <v>734450.49</v>
       </c>
       <c r="F42" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="G42">
-        <v>5000.8</v>
+        <v>734450.49</v>
       </c>
       <c r="I42" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
     </row>
     <row r="43" spans="1:9">
       <c r="A43" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B43" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C43" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D43" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="E43">
-        <v>5000.8</v>
+        <v>734450.49</v>
       </c>
       <c r="F43" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="G43">
-        <v>5000.8</v>
+        <v>734450.49</v>
       </c>
       <c r="I43" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
     </row>
     <row r="44" spans="1:9">
       <c r="A44" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B44" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C44" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D44" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E44">
-        <v>97.42</v>
+        <v>265786.66</v>
       </c>
       <c r="F44" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="G44">
-        <v>116.4</v>
+        <v>265786.66</v>
       </c>
       <c r="I44" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
     </row>
     <row r="45" spans="1:9">
       <c r="A45" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B45" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C45" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D45" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="E45">
-        <v>97.42</v>
+        <v>265786.66</v>
       </c>
       <c r="F45" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="G45">
-        <v>116.4</v>
+        <v>265786.66</v>
       </c>
       <c r="I45" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
     </row>
     <row r="46" spans="1:9">
       <c r="A46" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B46" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C46" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D46" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E46">
-        <v>18.98</v>
+        <v>30382.2</v>
       </c>
       <c r="F46" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="G46">
-        <v>116.4</v>
+        <v>30382.2</v>
       </c>
       <c r="I46" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
     </row>
     <row r="47" spans="1:9">
       <c r="A47" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B47" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C47" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D47" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="E47">
-        <v>18.98</v>
+        <v>30382.2</v>
       </c>
       <c r="F47" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G47">
-        <v>116.4</v>
+        <v>30382.2</v>
       </c>
       <c r="I47" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
     </row>
     <row r="48" spans="1:9">
       <c r="A48" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B48" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C48" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D48" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="E48">
-        <v>38501.38</v>
+        <v>1806</v>
       </c>
       <c r="F48" t="s">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="G48">
-        <v>105637.59</v>
+        <v>5664.64</v>
       </c>
       <c r="I48" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
     </row>
     <row r="49" spans="1:9">
       <c r="A49" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B49" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C49" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D49" t="s">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="E49">
-        <v>38501.38</v>
+        <v>1806</v>
       </c>
       <c r="F49" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="G49">
-        <v>105637.59</v>
+        <v>5664.64</v>
       </c>
       <c r="I49" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
     </row>
     <row r="50" spans="1:9">
       <c r="A50" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B50" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C50" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D50" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="E50">
-        <v>67136.21000000001</v>
+        <v>3858.64</v>
       </c>
       <c r="F50" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="G50">
-        <v>105637.59</v>
+        <v>5664.64</v>
       </c>
       <c r="I50" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
     </row>
     <row r="51" spans="1:9">
       <c r="A51" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B51" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C51" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D51" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="E51">
-        <v>67136.21000000001</v>
+        <v>3858.64</v>
       </c>
       <c r="F51" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="G51">
-        <v>105637.59</v>
+        <v>5664.64</v>
       </c>
       <c r="I51" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
     </row>
     <row r="52" spans="1:9">
@@ -1900,25 +1918,25 @@
         <v>21</v>
       </c>
       <c r="B52" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C52" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D52" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="E52">
-        <v>78461.92</v>
+        <v>25.07</v>
       </c>
       <c r="F52" t="s">
-        <v>57</v>
+        <v>36</v>
       </c>
       <c r="G52">
-        <v>78461.92</v>
+        <v>5000.8</v>
       </c>
       <c r="I52" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
     </row>
     <row r="53" spans="1:9">
@@ -1926,337 +1944,909 @@
         <v>21</v>
       </c>
       <c r="B53" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C53" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D53" t="s">
-        <v>57</v>
+        <v>36</v>
       </c>
       <c r="E53">
-        <v>78461.92</v>
+        <v>25.07</v>
       </c>
       <c r="F53" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="G53">
-        <v>78461.92</v>
+        <v>5000.8</v>
       </c>
       <c r="I53" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
     </row>
     <row r="54" spans="1:9">
       <c r="A54" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B54" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C54" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D54" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="E54">
-        <v>8287.23</v>
+        <v>4975.73</v>
       </c>
       <c r="F54" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="G54">
-        <v>8287.23</v>
+        <v>5000.8</v>
       </c>
       <c r="I54" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
     </row>
     <row r="55" spans="1:9">
       <c r="A55" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B55" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C55" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D55" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="E55">
-        <v>8287.23</v>
+        <v>4975.73</v>
       </c>
       <c r="F55" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G55">
-        <v>8287.23</v>
+        <v>5000.8</v>
       </c>
       <c r="I55" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
     </row>
     <row r="56" spans="1:9">
       <c r="A56" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B56" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="C56" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D56" t="s">
-        <v>33</v>
+        <v>56</v>
       </c>
       <c r="E56">
-        <v>1149.04</v>
+        <v>116.4</v>
       </c>
       <c r="F56" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G56">
-        <v>1149.04</v>
+        <v>116.4</v>
       </c>
       <c r="I56" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
     </row>
     <row r="57" spans="1:9">
       <c r="A57" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B57" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C57" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D57" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E57">
-        <v>1149.04</v>
+        <v>116.4</v>
       </c>
       <c r="F57" t="s">
-        <v>33</v>
+        <v>56</v>
       </c>
       <c r="G57">
-        <v>1149.04</v>
+        <v>116.4</v>
       </c>
       <c r="I57" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
     </row>
     <row r="58" spans="1:9">
       <c r="A58" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B58" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="C58" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D58" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E58">
-        <v>64401.82</v>
+        <v>32301.16</v>
       </c>
       <c r="F58" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="G58">
-        <v>64401.82</v>
+        <v>105637.59</v>
       </c>
       <c r="I58" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
     </row>
     <row r="59" spans="1:9">
       <c r="A59" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B59" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C59" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D59" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E59">
-        <v>64401.82</v>
+        <v>32301.16</v>
       </c>
       <c r="F59" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="G59">
-        <v>64401.82</v>
+        <v>105637.59</v>
       </c>
       <c r="I59" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
     </row>
     <row r="60" spans="1:9">
       <c r="A60" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B60" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="C60" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D60" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="E60">
-        <v>160118.05</v>
+        <v>97.42</v>
       </c>
       <c r="F60" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="G60">
-        <v>160118.05</v>
+        <v>105637.59</v>
       </c>
       <c r="I60" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
     </row>
     <row r="61" spans="1:9">
       <c r="A61" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B61" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="C61" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D61" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E61">
-        <v>160118.05</v>
+        <v>97.42</v>
       </c>
       <c r="F61" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="G61">
-        <v>160118.05</v>
+        <v>105637.59</v>
       </c>
       <c r="I61" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
     </row>
     <row r="62" spans="1:9">
       <c r="A62" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B62" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C62" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D62" t="s">
-        <v>32</v>
+        <v>57</v>
       </c>
       <c r="E62">
-        <v>135.08</v>
+        <v>38520.36</v>
       </c>
       <c r="F62" t="s">
-        <v>32</v>
+        <v>58</v>
       </c>
       <c r="G62">
-        <v>135.08</v>
+        <v>105637.59</v>
       </c>
       <c r="I62" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
     </row>
     <row r="63" spans="1:9">
       <c r="A63" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B63" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C63" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D63" t="s">
-        <v>32</v>
+        <v>58</v>
       </c>
       <c r="E63">
-        <v>135.08</v>
+        <v>38520.36</v>
       </c>
       <c r="F63" t="s">
-        <v>32</v>
+        <v>57</v>
       </c>
       <c r="G63">
-        <v>135.08</v>
+        <v>105637.59</v>
       </c>
       <c r="I63" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
     </row>
     <row r="64" spans="1:9">
       <c r="A64" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B64" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="C64" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D64" t="s">
-        <v>33</v>
+        <v>57</v>
       </c>
       <c r="E64">
-        <v>897.88</v>
+        <v>34718.65</v>
       </c>
       <c r="F64" t="s">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="G64">
-        <v>897.88</v>
+        <v>105637.59</v>
       </c>
       <c r="I64" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
     </row>
     <row r="65" spans="1:9">
       <c r="A65" t="s">
+        <v>22</v>
+      </c>
+      <c r="B65" t="s">
+        <v>32</v>
+      </c>
+      <c r="C65" t="s">
+        <v>34</v>
+      </c>
+      <c r="D65" t="s">
+        <v>59</v>
+      </c>
+      <c r="E65">
+        <v>34718.65</v>
+      </c>
+      <c r="F65" t="s">
+        <v>57</v>
+      </c>
+      <c r="G65">
+        <v>105637.59</v>
+      </c>
+      <c r="I65" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9">
+      <c r="A66" t="s">
+        <v>22</v>
+      </c>
+      <c r="B66" t="s">
+        <v>32</v>
+      </c>
+      <c r="C66" t="s">
+        <v>33</v>
+      </c>
+      <c r="D66" t="s">
+        <v>60</v>
+      </c>
+      <c r="E66">
+        <v>78461.92</v>
+      </c>
+      <c r="F66" t="s">
+        <v>59</v>
+      </c>
+      <c r="G66">
+        <v>78461.92</v>
+      </c>
+      <c r="I66" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9">
+      <c r="A67" t="s">
+        <v>22</v>
+      </c>
+      <c r="B67" t="s">
+        <v>32</v>
+      </c>
+      <c r="C67" t="s">
+        <v>34</v>
+      </c>
+      <c r="D67" t="s">
+        <v>59</v>
+      </c>
+      <c r="E67">
+        <v>78461.92</v>
+      </c>
+      <c r="F67" t="s">
+        <v>60</v>
+      </c>
+      <c r="G67">
+        <v>78461.92</v>
+      </c>
+      <c r="I67" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9">
+      <c r="A68" t="s">
+        <v>23</v>
+      </c>
+      <c r="B68" t="s">
+        <v>32</v>
+      </c>
+      <c r="C68" t="s">
+        <v>33</v>
+      </c>
+      <c r="D68" t="s">
+        <v>61</v>
+      </c>
+      <c r="E68">
+        <v>321.78</v>
+      </c>
+      <c r="F68" t="s">
+        <v>36</v>
+      </c>
+      <c r="G68">
+        <v>8287.23</v>
+      </c>
+      <c r="I68" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9">
+      <c r="A69" t="s">
+        <v>23</v>
+      </c>
+      <c r="B69" t="s">
+        <v>30</v>
+      </c>
+      <c r="C69" t="s">
+        <v>34</v>
+      </c>
+      <c r="D69" t="s">
+        <v>36</v>
+      </c>
+      <c r="E69">
+        <v>321.78</v>
+      </c>
+      <c r="F69" t="s">
+        <v>61</v>
+      </c>
+      <c r="G69">
+        <v>8287.23</v>
+      </c>
+      <c r="I69" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9">
+      <c r="A70" t="s">
+        <v>23</v>
+      </c>
+      <c r="B70" t="s">
+        <v>32</v>
+      </c>
+      <c r="C70" t="s">
+        <v>33</v>
+      </c>
+      <c r="D70" t="s">
+        <v>61</v>
+      </c>
+      <c r="E70">
+        <v>7965.45</v>
+      </c>
+      <c r="F70" t="s">
+        <v>62</v>
+      </c>
+      <c r="G70">
+        <v>8287.23</v>
+      </c>
+      <c r="I70" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9">
+      <c r="A71" t="s">
+        <v>23</v>
+      </c>
+      <c r="B71" t="s">
+        <v>32</v>
+      </c>
+      <c r="C71" t="s">
+        <v>34</v>
+      </c>
+      <c r="D71" t="s">
+        <v>62</v>
+      </c>
+      <c r="E71">
+        <v>7965.45</v>
+      </c>
+      <c r="F71" t="s">
+        <v>61</v>
+      </c>
+      <c r="G71">
+        <v>8287.23</v>
+      </c>
+      <c r="I71" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9">
+      <c r="A72" t="s">
+        <v>24</v>
+      </c>
+      <c r="B72" t="s">
+        <v>30</v>
+      </c>
+      <c r="C72" t="s">
+        <v>33</v>
+      </c>
+      <c r="D72" t="s">
+        <v>36</v>
+      </c>
+      <c r="E72">
+        <v>1149.04</v>
+      </c>
+      <c r="F72" t="s">
+        <v>41</v>
+      </c>
+      <c r="G72">
+        <v>1149.04</v>
+      </c>
+      <c r="I72" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9">
+      <c r="A73" t="s">
+        <v>24</v>
+      </c>
+      <c r="B73" t="s">
+        <v>30</v>
+      </c>
+      <c r="C73" t="s">
+        <v>34</v>
+      </c>
+      <c r="D73" t="s">
+        <v>41</v>
+      </c>
+      <c r="E73">
+        <v>1149.04</v>
+      </c>
+      <c r="F73" t="s">
+        <v>36</v>
+      </c>
+      <c r="G73">
+        <v>1149.04</v>
+      </c>
+      <c r="I73" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9">
+      <c r="A74" t="s">
         <v>25</v>
       </c>
-      <c r="B65" t="s">
+      <c r="B74" t="s">
+        <v>30</v>
+      </c>
+      <c r="C74" t="s">
+        <v>33</v>
+      </c>
+      <c r="D74" t="s">
+        <v>63</v>
+      </c>
+      <c r="E74">
+        <v>64401.82</v>
+      </c>
+      <c r="F74" t="s">
+        <v>36</v>
+      </c>
+      <c r="G74">
+        <v>64401.82</v>
+      </c>
+      <c r="I74" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9">
+      <c r="A75" t="s">
+        <v>25</v>
+      </c>
+      <c r="B75" t="s">
+        <v>30</v>
+      </c>
+      <c r="C75" t="s">
+        <v>34</v>
+      </c>
+      <c r="D75" t="s">
+        <v>36</v>
+      </c>
+      <c r="E75">
+        <v>64401.82</v>
+      </c>
+      <c r="F75" t="s">
+        <v>63</v>
+      </c>
+      <c r="G75">
+        <v>64401.82</v>
+      </c>
+      <c r="I75" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9">
+      <c r="A76" t="s">
+        <v>25</v>
+      </c>
+      <c r="B76" t="s">
+        <v>30</v>
+      </c>
+      <c r="C76" t="s">
+        <v>33</v>
+      </c>
+      <c r="D76" t="s">
+        <v>64</v>
+      </c>
+      <c r="E76">
+        <v>160118.05</v>
+      </c>
+      <c r="F76" t="s">
+        <v>36</v>
+      </c>
+      <c r="G76">
+        <v>160118.05</v>
+      </c>
+      <c r="I76" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9">
+      <c r="A77" t="s">
+        <v>25</v>
+      </c>
+      <c r="B77" t="s">
+        <v>30</v>
+      </c>
+      <c r="C77" t="s">
+        <v>34</v>
+      </c>
+      <c r="D77" t="s">
+        <v>36</v>
+      </c>
+      <c r="E77">
+        <v>160118.05</v>
+      </c>
+      <c r="F77" t="s">
+        <v>64</v>
+      </c>
+      <c r="G77">
+        <v>160118.05</v>
+      </c>
+      <c r="I77" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9">
+      <c r="A78" t="s">
+        <v>25</v>
+      </c>
+      <c r="B78" t="s">
+        <v>29</v>
+      </c>
+      <c r="C78" t="s">
+        <v>33</v>
+      </c>
+      <c r="D78" t="s">
+        <v>35</v>
+      </c>
+      <c r="E78">
+        <v>135.08</v>
+      </c>
+      <c r="F78" t="s">
+        <v>36</v>
+      </c>
+      <c r="G78">
+        <v>135.08</v>
+      </c>
+      <c r="I78" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9">
+      <c r="A79" t="s">
+        <v>25</v>
+      </c>
+      <c r="B79" t="s">
+        <v>30</v>
+      </c>
+      <c r="C79" t="s">
+        <v>34</v>
+      </c>
+      <c r="D79" t="s">
+        <v>36</v>
+      </c>
+      <c r="E79">
+        <v>135.08</v>
+      </c>
+      <c r="F79" t="s">
+        <v>35</v>
+      </c>
+      <c r="G79">
+        <v>135.08</v>
+      </c>
+      <c r="I79" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9">
+      <c r="A80" t="s">
+        <v>26</v>
+      </c>
+      <c r="B80" t="s">
+        <v>32</v>
+      </c>
+      <c r="C80" t="s">
+        <v>33</v>
+      </c>
+      <c r="D80" t="s">
+        <v>65</v>
+      </c>
+      <c r="E80">
+        <v>2577.61</v>
+      </c>
+      <c r="F80" t="s">
+        <v>36</v>
+      </c>
+      <c r="G80">
+        <v>204151.77</v>
+      </c>
+      <c r="I80" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9">
+      <c r="A81" t="s">
+        <v>26</v>
+      </c>
+      <c r="B81" t="s">
+        <v>30</v>
+      </c>
+      <c r="C81" t="s">
+        <v>34</v>
+      </c>
+      <c r="D81" t="s">
+        <v>36</v>
+      </c>
+      <c r="E81">
+        <v>2577.61</v>
+      </c>
+      <c r="F81" t="s">
+        <v>65</v>
+      </c>
+      <c r="G81">
+        <v>204151.77</v>
+      </c>
+      <c r="I81" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9">
+      <c r="A82" t="s">
         <v>27</v>
       </c>
-      <c r="C65" t="s">
-        <v>31</v>
-      </c>
-      <c r="D65" t="s">
-        <v>33</v>
-      </c>
-      <c r="E65">
+      <c r="B82" t="s">
+        <v>32</v>
+      </c>
+      <c r="C82" t="s">
+        <v>33</v>
+      </c>
+      <c r="D82" t="s">
+        <v>66</v>
+      </c>
+      <c r="E82">
+        <v>1703.99</v>
+      </c>
+      <c r="F82" t="s">
+        <v>36</v>
+      </c>
+      <c r="G82">
+        <v>126570.33</v>
+      </c>
+      <c r="I82" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9">
+      <c r="A83" t="s">
+        <v>27</v>
+      </c>
+      <c r="B83" t="s">
+        <v>30</v>
+      </c>
+      <c r="C83" t="s">
+        <v>34</v>
+      </c>
+      <c r="D83" t="s">
+        <v>36</v>
+      </c>
+      <c r="E83">
+        <v>1703.99</v>
+      </c>
+      <c r="F83" t="s">
+        <v>66</v>
+      </c>
+      <c r="G83">
+        <v>126570.33</v>
+      </c>
+      <c r="I83" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9">
+      <c r="A84" t="s">
+        <v>28</v>
+      </c>
+      <c r="B84" t="s">
+        <v>30</v>
+      </c>
+      <c r="C84" t="s">
+        <v>33</v>
+      </c>
+      <c r="D84" t="s">
+        <v>36</v>
+      </c>
+      <c r="E84">
         <v>897.88</v>
       </c>
-      <c r="F65" t="s">
-        <v>33</v>
-      </c>
-      <c r="G65">
+      <c r="F84" t="s">
+        <v>36</v>
+      </c>
+      <c r="G84">
         <v>897.88</v>
       </c>
-      <c r="I65" t="s">
-        <v>62</v>
+      <c r="I84" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9">
+      <c r="A85" t="s">
+        <v>28</v>
+      </c>
+      <c r="B85" t="s">
+        <v>30</v>
+      </c>
+      <c r="C85" t="s">
+        <v>34</v>
+      </c>
+      <c r="D85" t="s">
+        <v>36</v>
+      </c>
+      <c r="E85">
+        <v>897.88</v>
+      </c>
+      <c r="F85" t="s">
+        <v>36</v>
+      </c>
+      <c r="G85">
+        <v>897.88</v>
+      </c>
+      <c r="I85" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9">
+      <c r="A86" t="s">
+        <v>28</v>
+      </c>
+      <c r="B86" t="s">
+        <v>32</v>
+      </c>
+      <c r="C86" t="s">
+        <v>33</v>
+      </c>
+      <c r="D86" t="s">
+        <v>67</v>
+      </c>
+      <c r="E86">
+        <v>1005.5</v>
+      </c>
+      <c r="F86" t="s">
+        <v>36</v>
+      </c>
+      <c r="G86">
+        <v>1754.18</v>
+      </c>
+      <c r="I86" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9">
+      <c r="A87" t="s">
+        <v>28</v>
+      </c>
+      <c r="B87" t="s">
+        <v>30</v>
+      </c>
+      <c r="C87" t="s">
+        <v>34</v>
+      </c>
+      <c r="D87" t="s">
+        <v>36</v>
+      </c>
+      <c r="E87">
+        <v>1005.5</v>
+      </c>
+      <c r="F87" t="s">
+        <v>67</v>
+      </c>
+      <c r="G87">
+        <v>1754.18</v>
+      </c>
+      <c r="I87" t="s">
+        <v>68</v>
       </c>
     </row>
   </sheetData>

--- a/planilha_transferencias_audesp.xlsx
+++ b/planilha_transferencias_audesp.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="526" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="526" uniqueCount="54">
   <si>
     <t>FICHA</t>
   </si>
@@ -46,63 +46,6 @@
     <t>MENSAGEM</t>
   </si>
   <si>
-    <t>1210</t>
-  </si>
-  <si>
-    <t>1240</t>
-  </si>
-  <si>
-    <t>1268</t>
-  </si>
-  <si>
-    <t>1297</t>
-  </si>
-  <si>
-    <t>1311</t>
-  </si>
-  <si>
-    <t>1399</t>
-  </si>
-  <si>
-    <t>1414</t>
-  </si>
-  <si>
-    <t>1421</t>
-  </si>
-  <si>
-    <t>1438</t>
-  </si>
-  <si>
-    <t>1442</t>
-  </si>
-  <si>
-    <t>1463</t>
-  </si>
-  <si>
-    <t>1479</t>
-  </si>
-  <si>
-    <t>1481</t>
-  </si>
-  <si>
-    <t>1486</t>
-  </si>
-  <si>
-    <t>1490</t>
-  </si>
-  <si>
-    <t>1498</t>
-  </si>
-  <si>
-    <t>1514</t>
-  </si>
-  <si>
-    <t>1515</t>
-  </si>
-  <si>
-    <t>1516</t>
-  </si>
-  <si>
     <t>19 - RECURSOS EXTRAÓRÇAMENTÁRIOS</t>
   </si>
   <si>
@@ -220,7 +163,31 @@
     <t>800.0005 - Emenda N° 36000654021202500 - Dp. Jonas Donizete</t>
   </si>
   <si>
-    <t>PENDENTE</t>
+    <t>ERRO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Locator.wait_for: Timeout 10000ms exceeded.
+Call log:
+  - waiting for locator("input.dx-texteditor-input[role='combobox']").first to be visible
+    23 × locator resolved to hidden &lt;input readonly type="text" tabindex="0" role="combobox" spellcheck="false" aria-expanded="false" aria-haspopup="listbox" aria-autocomplete="none" autocomplete="chrome-off" placeholder="Selecione ..." class="dx-texteditor-input" aria-owns="dx-b859372f-fc19-69ca-31c3-1bc2d4208574" aria-controls="dx-19652cef-5c23-0195-d93d-67180546bd66"/&gt;
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Locator.wait_for: Timeout 30000ms exceeded.
+Call log:
+  - waiting for locator("span.dx-button-text:has-text('Novo')").first to be visible
+    62 × locator resolved to hidden &lt;span class="dx-button-text"&gt;Novo&lt;/span&gt;
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Locator.wait_for: Target page, context or browser has been closed
+Call log:
+  - waiting for locator("span.dx-button-text:has-text('Novo')").first to be visible
+    56 × locator resolved to hidden &lt;span class="dx-button-text"&gt;Novo&lt;/span&gt;
+</t>
+  </si>
+  <si>
+    <t>Locator.wait_for: Target page, context or browser has been closed</t>
   </si>
 </sst>
 </file>
@@ -614,2239 +581,2497 @@
       </c>
     </row>
     <row r="2" spans="1:10">
-      <c r="A2" t="s">
+      <c r="A2">
+        <v>1210</v>
+      </c>
+      <c r="B2" t="s">
         <v>10</v>
       </c>
-      <c r="B2" t="s">
-        <v>29</v>
-      </c>
       <c r="C2" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="D2" t="s">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="E2">
         <v>45.54</v>
       </c>
       <c r="F2" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="G2">
         <v>45.54</v>
       </c>
       <c r="I2" t="s">
-        <v>68</v>
+        <v>49</v>
+      </c>
+      <c r="J2" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:10">
-      <c r="A3" t="s">
-        <v>10</v>
+      <c r="A3">
+        <v>1210</v>
       </c>
       <c r="B3" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="C3" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="D3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="E3">
         <v>45.54</v>
       </c>
       <c r="F3" t="s">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="G3">
         <v>45.54</v>
       </c>
       <c r="I3" t="s">
-        <v>68</v>
+        <v>49</v>
+      </c>
+      <c r="J3" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:10">
-      <c r="A4" t="s">
-        <v>11</v>
+      <c r="A4">
+        <v>1240</v>
       </c>
       <c r="B4" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="C4" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="D4" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="E4">
         <v>938.17</v>
       </c>
       <c r="F4" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="G4">
         <v>938.17</v>
       </c>
       <c r="I4" t="s">
-        <v>68</v>
+        <v>49</v>
+      </c>
+      <c r="J4" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="5" spans="1:10">
-      <c r="A5" t="s">
-        <v>11</v>
+      <c r="A5">
+        <v>1240</v>
       </c>
       <c r="B5" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="C5" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="D5" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="E5">
         <v>938.17</v>
       </c>
       <c r="F5" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="G5">
         <v>938.17</v>
       </c>
       <c r="I5" t="s">
-        <v>68</v>
+        <v>49</v>
+      </c>
+      <c r="J5" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="6" spans="1:10">
-      <c r="A6" t="s">
-        <v>11</v>
+      <c r="A6">
+        <v>1240</v>
       </c>
       <c r="B6" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="C6" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="D6" t="s">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="E6">
         <v>70429.23</v>
       </c>
       <c r="F6" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="G6">
         <v>93832.32000000001</v>
       </c>
       <c r="I6" t="s">
-        <v>68</v>
+        <v>49</v>
+      </c>
+      <c r="J6" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="7" spans="1:10">
-      <c r="A7" t="s">
-        <v>11</v>
+      <c r="A7">
+        <v>1240</v>
       </c>
       <c r="B7" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="C7" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="D7" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="E7">
         <v>70429.23</v>
       </c>
       <c r="F7" t="s">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="G7">
         <v>93832.32000000001</v>
       </c>
       <c r="I7" t="s">
-        <v>68</v>
+        <v>49</v>
+      </c>
+      <c r="J7" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="8" spans="1:10">
-      <c r="A8" t="s">
-        <v>11</v>
+      <c r="A8">
+        <v>1240</v>
       </c>
       <c r="B8" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="C8" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="D8" t="s">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="E8">
         <v>251.42</v>
       </c>
       <c r="F8" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="G8">
         <v>93832.32000000001</v>
       </c>
       <c r="I8" t="s">
-        <v>68</v>
+        <v>49</v>
+      </c>
+      <c r="J8" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="9" spans="1:10">
-      <c r="A9" t="s">
-        <v>11</v>
+      <c r="A9">
+        <v>1240</v>
       </c>
       <c r="B9" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="C9" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="D9" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="E9">
         <v>251.42</v>
       </c>
       <c r="F9" t="s">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="G9">
         <v>93832.32000000001</v>
       </c>
       <c r="I9" t="s">
-        <v>68</v>
+        <v>49</v>
+      </c>
+      <c r="J9" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="10" spans="1:10">
-      <c r="A10" t="s">
-        <v>11</v>
+      <c r="A10">
+        <v>1240</v>
       </c>
       <c r="B10" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="C10" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="D10" t="s">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="E10">
         <v>23151.67</v>
       </c>
       <c r="F10" t="s">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="G10">
         <v>93832.32000000001</v>
       </c>
       <c r="I10" t="s">
-        <v>68</v>
+        <v>49</v>
+      </c>
+      <c r="J10" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="11" spans="1:10">
-      <c r="A11" t="s">
-        <v>11</v>
+      <c r="A11">
+        <v>1240</v>
       </c>
       <c r="B11" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="C11" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="D11" t="s">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="E11">
         <v>23151.67</v>
       </c>
       <c r="F11" t="s">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="G11">
         <v>93832.32000000001</v>
       </c>
       <c r="I11" t="s">
-        <v>68</v>
+        <v>49</v>
+      </c>
+      <c r="J11" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="12" spans="1:10">
-      <c r="A12" t="s">
-        <v>11</v>
+      <c r="A12">
+        <v>1240</v>
       </c>
       <c r="B12" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="C12" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="D12" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="E12">
         <v>77631.55</v>
       </c>
       <c r="F12" t="s">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="G12">
         <v>77631.55</v>
       </c>
       <c r="I12" t="s">
-        <v>68</v>
+        <v>49</v>
+      </c>
+      <c r="J12" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="13" spans="1:10">
-      <c r="A13" t="s">
-        <v>11</v>
+      <c r="A13">
+        <v>1240</v>
       </c>
       <c r="B13" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="C13" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="D13" t="s">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="E13">
         <v>77631.55</v>
       </c>
       <c r="F13" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="G13">
         <v>77631.55</v>
       </c>
       <c r="I13" t="s">
-        <v>68</v>
+        <v>49</v>
+      </c>
+      <c r="J13" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="14" spans="1:10">
-      <c r="A14" t="s">
-        <v>11</v>
+      <c r="A14">
+        <v>1240</v>
       </c>
       <c r="B14" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="C14" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="D14" t="s">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="E14">
         <v>9697.799999999999</v>
       </c>
       <c r="F14" t="s">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="G14">
         <v>9697.799999999999</v>
       </c>
       <c r="I14" t="s">
-        <v>68</v>
+        <v>49</v>
+      </c>
+      <c r="J14" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="15" spans="1:10">
-      <c r="A15" t="s">
-        <v>11</v>
+      <c r="A15">
+        <v>1240</v>
       </c>
       <c r="B15" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="C15" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="D15" t="s">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="E15">
         <v>9697.799999999999</v>
       </c>
       <c r="F15" t="s">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="G15">
         <v>9697.799999999999</v>
       </c>
       <c r="I15" t="s">
-        <v>68</v>
+        <v>49</v>
+      </c>
+      <c r="J15" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="16" spans="1:10">
-      <c r="A16" t="s">
-        <v>12</v>
+      <c r="A16">
+        <v>1268</v>
       </c>
       <c r="B16" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="C16" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="D16" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="E16">
         <v>5063.53</v>
       </c>
       <c r="F16" t="s">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="G16">
         <v>5063.53</v>
       </c>
       <c r="I16" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9">
-      <c r="A17" t="s">
-        <v>12</v>
+        <v>49</v>
+      </c>
+      <c r="J16" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
+      <c r="A17">
+        <v>1268</v>
       </c>
       <c r="B17" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="C17" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="D17" t="s">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="E17">
         <v>5063.53</v>
       </c>
       <c r="F17" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="G17">
         <v>5063.53</v>
       </c>
       <c r="I17" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9">
-      <c r="A18" t="s">
-        <v>13</v>
+        <v>49</v>
+      </c>
+      <c r="J17" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
+      <c r="A18">
+        <v>1297</v>
       </c>
       <c r="B18" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="C18" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="D18" t="s">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="E18">
         <v>1446.48</v>
       </c>
       <c r="F18" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="G18">
         <v>1446.48</v>
       </c>
       <c r="I18" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9">
-      <c r="A19" t="s">
-        <v>13</v>
+        <v>49</v>
+      </c>
+      <c r="J18" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
+      <c r="A19">
+        <v>1297</v>
       </c>
       <c r="B19" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="C19" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="D19" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="E19">
         <v>1446.48</v>
       </c>
       <c r="F19" t="s">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="G19">
         <v>1446.48</v>
       </c>
       <c r="I19" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9">
-      <c r="A20" t="s">
-        <v>14</v>
+        <v>49</v>
+      </c>
+      <c r="J19" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
+      <c r="A20">
+        <v>1311</v>
       </c>
       <c r="B20" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="C20" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="D20" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="E20">
         <v>18952.13</v>
       </c>
       <c r="F20" t="s">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="G20">
         <v>18952.13</v>
       </c>
       <c r="I20" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9">
-      <c r="A21" t="s">
-        <v>14</v>
+        <v>49</v>
+      </c>
+      <c r="J20" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
+      <c r="A21">
+        <v>1311</v>
       </c>
       <c r="B21" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="C21" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="D21" t="s">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="E21">
         <v>18952.13</v>
       </c>
       <c r="F21" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="G21">
         <v>18952.13</v>
       </c>
       <c r="I21" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9">
-      <c r="A22" t="s">
-        <v>15</v>
+        <v>49</v>
+      </c>
+      <c r="J21" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
+      <c r="A22">
+        <v>1399</v>
       </c>
       <c r="B22" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="C22" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="D22" t="s">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="E22">
         <v>3566.46</v>
       </c>
       <c r="F22" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="G22">
         <v>4403.17</v>
       </c>
       <c r="I22" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9">
-      <c r="A23" t="s">
-        <v>15</v>
+        <v>49</v>
+      </c>
+      <c r="J22" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10">
+      <c r="A23">
+        <v>1399</v>
       </c>
       <c r="B23" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="C23" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="D23" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="E23">
         <v>3566.46</v>
       </c>
       <c r="F23" t="s">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="G23">
         <v>4403.17</v>
       </c>
       <c r="I23" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9">
-      <c r="A24" t="s">
-        <v>15</v>
+        <v>49</v>
+      </c>
+      <c r="J23" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10">
+      <c r="A24">
+        <v>1399</v>
       </c>
       <c r="B24" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="C24" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="D24" t="s">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="E24">
         <v>836.71</v>
       </c>
       <c r="F24" t="s">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="G24">
         <v>4403.17</v>
       </c>
       <c r="I24" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9">
-      <c r="A25" t="s">
-        <v>15</v>
+        <v>49</v>
+      </c>
+      <c r="J24" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10">
+      <c r="A25">
+        <v>1399</v>
       </c>
       <c r="B25" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="C25" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="D25" t="s">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="E25">
         <v>836.71</v>
       </c>
       <c r="F25" t="s">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="G25">
         <v>4403.17</v>
       </c>
       <c r="I25" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9">
-      <c r="A26" t="s">
-        <v>16</v>
+        <v>49</v>
+      </c>
+      <c r="J25" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10">
+      <c r="A26">
+        <v>1414</v>
       </c>
       <c r="B26" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="C26" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="D26" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="E26">
         <v>17031.81</v>
       </c>
       <c r="F26" t="s">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="G26">
         <v>17031.81</v>
       </c>
       <c r="I26" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9">
-      <c r="A27" t="s">
-        <v>16</v>
+        <v>49</v>
+      </c>
+      <c r="J26" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10">
+      <c r="A27">
+        <v>1414</v>
       </c>
       <c r="B27" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="C27" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="D27" t="s">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="E27">
         <v>17031.81</v>
       </c>
       <c r="F27" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="G27">
         <v>17031.81</v>
       </c>
       <c r="I27" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9">
-      <c r="A28" t="s">
-        <v>17</v>
+        <v>49</v>
+      </c>
+      <c r="J27" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10">
+      <c r="A28">
+        <v>1421</v>
       </c>
       <c r="B28" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="C28" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="D28" t="s">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="E28">
         <v>1663.2</v>
       </c>
       <c r="F28" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="G28">
         <v>1663.2</v>
       </c>
       <c r="I28" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9">
-      <c r="A29" t="s">
-        <v>17</v>
+        <v>49</v>
+      </c>
+      <c r="J28" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10">
+      <c r="A29">
+        <v>1421</v>
       </c>
       <c r="B29" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="C29" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="D29" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="E29">
         <v>1663.2</v>
       </c>
       <c r="F29" t="s">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="G29">
         <v>1663.2</v>
       </c>
       <c r="I29" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9">
-      <c r="A30" t="s">
-        <v>17</v>
+        <v>49</v>
+      </c>
+      <c r="J29" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10">
+      <c r="A30">
+        <v>1421</v>
       </c>
       <c r="B30" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="C30" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="D30" t="s">
-        <v>46</v>
+        <v>27</v>
       </c>
       <c r="E30">
         <v>325.67</v>
       </c>
       <c r="F30" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="G30">
         <v>123821.82</v>
       </c>
       <c r="I30" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9">
-      <c r="A31" t="s">
-        <v>17</v>
+        <v>49</v>
+      </c>
+      <c r="J30" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10">
+      <c r="A31">
+        <v>1421</v>
       </c>
       <c r="B31" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="C31" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="D31" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="E31">
         <v>325.67</v>
       </c>
       <c r="F31" t="s">
-        <v>46</v>
+        <v>27</v>
       </c>
       <c r="G31">
         <v>123821.82</v>
       </c>
       <c r="I31" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9">
-      <c r="A32" t="s">
-        <v>17</v>
+        <v>49</v>
+      </c>
+      <c r="J31" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10">
+      <c r="A32">
+        <v>1421</v>
       </c>
       <c r="B32" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="C32" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="D32" t="s">
-        <v>46</v>
+        <v>27</v>
       </c>
       <c r="E32">
         <v>123496.15</v>
       </c>
       <c r="F32" t="s">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="G32">
         <v>123821.82</v>
       </c>
       <c r="I32" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9">
-      <c r="A33" t="s">
-        <v>17</v>
+        <v>49</v>
+      </c>
+      <c r="J32" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10">
+      <c r="A33">
+        <v>1421</v>
       </c>
       <c r="B33" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="C33" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="D33" t="s">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="E33">
         <v>123496.15</v>
       </c>
       <c r="F33" t="s">
-        <v>46</v>
+        <v>27</v>
       </c>
       <c r="G33">
         <v>123821.82</v>
       </c>
       <c r="I33" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9">
-      <c r="A34" t="s">
-        <v>18</v>
+        <v>49</v>
+      </c>
+      <c r="J33" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10">
+      <c r="A34">
+        <v>1438</v>
       </c>
       <c r="B34" t="s">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="C34" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="D34" t="s">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="E34">
         <v>108347.67</v>
       </c>
       <c r="F34" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="G34">
         <v>108347.67</v>
       </c>
       <c r="I34" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9">
-      <c r="A35" t="s">
-        <v>18</v>
+        <v>49</v>
+      </c>
+      <c r="J34" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10">
+      <c r="A35">
+        <v>1438</v>
       </c>
       <c r="B35" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="C35" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="D35" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="E35">
         <v>108347.67</v>
       </c>
       <c r="F35" t="s">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="G35">
         <v>108347.67</v>
       </c>
       <c r="I35" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9">
-      <c r="A36" t="s">
-        <v>19</v>
+        <v>49</v>
+      </c>
+      <c r="J35" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10">
+      <c r="A36">
+        <v>1442</v>
       </c>
       <c r="B36" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="C36" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="D36" t="s">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="E36">
         <v>742117.09</v>
       </c>
       <c r="F36" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="G36">
         <v>1461234.24</v>
       </c>
       <c r="I36" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9">
-      <c r="A37" t="s">
-        <v>19</v>
+        <v>49</v>
+      </c>
+      <c r="J36" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10">
+      <c r="A37">
+        <v>1442</v>
       </c>
       <c r="B37" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="C37" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="D37" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="E37">
         <v>742117.09</v>
       </c>
       <c r="F37" t="s">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="G37">
         <v>1461234.24</v>
       </c>
       <c r="I37" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9">
-      <c r="A38" t="s">
-        <v>19</v>
+        <v>49</v>
+      </c>
+      <c r="J37" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10">
+      <c r="A38">
+        <v>1442</v>
       </c>
       <c r="B38" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="C38" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="D38" t="s">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="E38">
         <v>719117.15</v>
       </c>
       <c r="F38" t="s">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="G38">
         <v>1461234.24</v>
       </c>
       <c r="I38" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9">
-      <c r="A39" t="s">
-        <v>19</v>
+        <v>49</v>
+      </c>
+      <c r="J38" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10">
+      <c r="A39">
+        <v>1442</v>
       </c>
       <c r="B39" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="C39" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="D39" t="s">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="E39">
         <v>719117.15</v>
       </c>
       <c r="F39" t="s">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="G39">
         <v>1461234.24</v>
       </c>
       <c r="I39" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9">
-      <c r="A40" t="s">
-        <v>19</v>
+        <v>49</v>
+      </c>
+      <c r="J39" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10">
+      <c r="A40">
+        <v>1442</v>
       </c>
       <c r="B40" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="C40" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="D40" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="E40">
         <v>551292.54</v>
       </c>
       <c r="F40" t="s">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="G40">
         <v>551292.54</v>
       </c>
       <c r="I40" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9">
-      <c r="A41" t="s">
-        <v>19</v>
+        <v>49</v>
+      </c>
+      <c r="J40" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10">
+      <c r="A41">
+        <v>1442</v>
       </c>
       <c r="B41" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="C41" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="D41" t="s">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="E41">
         <v>551292.54</v>
       </c>
       <c r="F41" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="G41">
         <v>551292.54</v>
       </c>
       <c r="I41" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9">
-      <c r="A42" t="s">
-        <v>19</v>
+        <v>49</v>
+      </c>
+      <c r="J41" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10">
+      <c r="A42">
+        <v>1442</v>
       </c>
       <c r="B42" t="s">
+        <v>12</v>
+      </c>
+      <c r="C42" t="s">
+        <v>14</v>
+      </c>
+      <c r="D42" t="s">
         <v>31</v>
-      </c>
-      <c r="C42" t="s">
-        <v>33</v>
-      </c>
-      <c r="D42" t="s">
-        <v>50</v>
       </c>
       <c r="E42">
         <v>734450.49</v>
       </c>
       <c r="F42" t="s">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="G42">
         <v>734450.49</v>
       </c>
       <c r="I42" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="43" spans="1:9">
-      <c r="A43" t="s">
-        <v>19</v>
+        <v>49</v>
+      </c>
+      <c r="J42" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10">
+      <c r="A43">
+        <v>1442</v>
       </c>
       <c r="B43" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="C43" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="D43" t="s">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="E43">
         <v>734450.49</v>
       </c>
       <c r="F43" t="s">
-        <v>50</v>
+        <v>31</v>
       </c>
       <c r="G43">
         <v>734450.49</v>
       </c>
       <c r="I43" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9">
-      <c r="A44" t="s">
-        <v>19</v>
+        <v>49</v>
+      </c>
+      <c r="J43" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10">
+      <c r="A44">
+        <v>1442</v>
       </c>
       <c r="B44" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="C44" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="D44" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="E44">
         <v>265786.66</v>
       </c>
       <c r="F44" t="s">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="G44">
         <v>265786.66</v>
       </c>
       <c r="I44" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="45" spans="1:9">
-      <c r="A45" t="s">
-        <v>19</v>
+        <v>49</v>
+      </c>
+      <c r="J44" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10">
+      <c r="A45">
+        <v>1442</v>
       </c>
       <c r="B45" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="C45" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="D45" t="s">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="E45">
         <v>265786.66</v>
       </c>
       <c r="F45" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="G45">
         <v>265786.66</v>
       </c>
       <c r="I45" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="46" spans="1:9">
-      <c r="A46" t="s">
-        <v>19</v>
+        <v>49</v>
+      </c>
+      <c r="J45" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10">
+      <c r="A46">
+        <v>1442</v>
       </c>
       <c r="B46" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="C46" t="s">
+        <v>14</v>
+      </c>
+      <c r="D46" t="s">
         <v>33</v>
-      </c>
-      <c r="D46" t="s">
-        <v>52</v>
       </c>
       <c r="E46">
         <v>30382.2</v>
       </c>
       <c r="F46" t="s">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="G46">
         <v>30382.2</v>
       </c>
       <c r="I46" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="47" spans="1:9">
-      <c r="A47" t="s">
-        <v>19</v>
+        <v>49</v>
+      </c>
+      <c r="J46" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10">
+      <c r="A47">
+        <v>1442</v>
       </c>
       <c r="B47" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="C47" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="D47" t="s">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="E47">
         <v>30382.2</v>
       </c>
       <c r="F47" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="G47">
         <v>30382.2</v>
       </c>
       <c r="I47" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="48" spans="1:9">
-      <c r="A48" t="s">
-        <v>20</v>
+        <v>49</v>
+      </c>
+      <c r="J47" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10">
+      <c r="A48">
+        <v>1463</v>
       </c>
       <c r="B48" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="C48" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="D48" t="s">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="E48">
         <v>1806</v>
       </c>
       <c r="F48" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="G48">
         <v>5664.64</v>
       </c>
       <c r="I48" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="49" spans="1:9">
-      <c r="A49" t="s">
-        <v>20</v>
+        <v>49</v>
+      </c>
+      <c r="J48" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10">
+      <c r="A49">
+        <v>1463</v>
       </c>
       <c r="B49" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="C49" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="D49" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="E49">
         <v>1806</v>
       </c>
       <c r="F49" t="s">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="G49">
         <v>5664.64</v>
       </c>
       <c r="I49" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="50" spans="1:9">
-      <c r="A50" t="s">
-        <v>20</v>
+        <v>49</v>
+      </c>
+      <c r="J49" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10">
+      <c r="A50">
+        <v>1463</v>
       </c>
       <c r="B50" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="C50" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="D50" t="s">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="E50">
         <v>3858.64</v>
       </c>
       <c r="F50" t="s">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="G50">
         <v>5664.64</v>
       </c>
       <c r="I50" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="51" spans="1:9">
-      <c r="A51" t="s">
-        <v>20</v>
+        <v>49</v>
+      </c>
+      <c r="J50" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10">
+      <c r="A51">
+        <v>1463</v>
       </c>
       <c r="B51" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="C51" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="D51" t="s">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="E51">
         <v>3858.64</v>
       </c>
       <c r="F51" t="s">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="G51">
         <v>5664.64</v>
       </c>
       <c r="I51" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="52" spans="1:9">
-      <c r="A52" t="s">
-        <v>21</v>
+        <v>49</v>
+      </c>
+      <c r="J51" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10">
+      <c r="A52">
+        <v>1479</v>
       </c>
       <c r="B52" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="C52" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="D52" t="s">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="E52">
         <v>25.07</v>
       </c>
       <c r="F52" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="G52">
         <v>5000.8</v>
       </c>
       <c r="I52" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="53" spans="1:9">
-      <c r="A53" t="s">
-        <v>21</v>
+        <v>49</v>
+      </c>
+      <c r="J52" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10">
+      <c r="A53">
+        <v>1479</v>
       </c>
       <c r="B53" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="C53" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="D53" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="E53">
         <v>25.07</v>
       </c>
       <c r="F53" t="s">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="G53">
         <v>5000.8</v>
       </c>
       <c r="I53" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="54" spans="1:9">
-      <c r="A54" t="s">
-        <v>21</v>
+        <v>49</v>
+      </c>
+      <c r="J53" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10">
+      <c r="A54">
+        <v>1479</v>
       </c>
       <c r="B54" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="C54" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="D54" t="s">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="E54">
         <v>4975.73</v>
       </c>
       <c r="F54" t="s">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="G54">
         <v>5000.8</v>
       </c>
       <c r="I54" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="55" spans="1:9">
-      <c r="A55" t="s">
-        <v>21</v>
+        <v>49</v>
+      </c>
+      <c r="J54" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10">
+      <c r="A55">
+        <v>1479</v>
       </c>
       <c r="B55" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="C55" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="D55" t="s">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="E55">
         <v>4975.73</v>
       </c>
       <c r="F55" t="s">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="G55">
         <v>5000.8</v>
       </c>
       <c r="I55" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="56" spans="1:9">
-      <c r="A56" t="s">
-        <v>22</v>
+        <v>49</v>
+      </c>
+      <c r="J55" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10">
+      <c r="A56">
+        <v>1481</v>
       </c>
       <c r="B56" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="C56" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="D56" t="s">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="E56">
         <v>116.4</v>
       </c>
       <c r="F56" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="G56">
         <v>116.4</v>
       </c>
       <c r="I56" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="57" spans="1:9">
-      <c r="A57" t="s">
-        <v>22</v>
+        <v>49</v>
+      </c>
+      <c r="J56" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10">
+      <c r="A57">
+        <v>1481</v>
       </c>
       <c r="B57" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="C57" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="D57" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="E57">
         <v>116.4</v>
       </c>
       <c r="F57" t="s">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="G57">
         <v>116.4</v>
       </c>
       <c r="I57" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="58" spans="1:9">
-      <c r="A58" t="s">
-        <v>22</v>
+        <v>49</v>
+      </c>
+      <c r="J57" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10">
+      <c r="A58">
+        <v>1481</v>
       </c>
       <c r="B58" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="C58" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="D58" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="E58">
         <v>32301.16</v>
       </c>
       <c r="F58" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="G58">
         <v>105637.59</v>
       </c>
       <c r="I58" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="59" spans="1:9">
-      <c r="A59" t="s">
-        <v>22</v>
+        <v>49</v>
+      </c>
+      <c r="J58" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10">
+      <c r="A59">
+        <v>1481</v>
       </c>
       <c r="B59" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="C59" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="D59" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="E59">
         <v>32301.16</v>
       </c>
       <c r="F59" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="G59">
         <v>105637.59</v>
       </c>
       <c r="I59" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="60" spans="1:9">
-      <c r="A60" t="s">
-        <v>22</v>
+        <v>49</v>
+      </c>
+      <c r="J59" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10">
+      <c r="A60">
+        <v>1481</v>
       </c>
       <c r="B60" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="C60" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="D60" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="E60">
         <v>97.42</v>
       </c>
       <c r="F60" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="G60">
         <v>105637.59</v>
       </c>
       <c r="I60" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="61" spans="1:9">
-      <c r="A61" t="s">
-        <v>22</v>
+        <v>49</v>
+      </c>
+      <c r="J60" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10">
+      <c r="A61">
+        <v>1481</v>
       </c>
       <c r="B61" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="C61" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="D61" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="E61">
         <v>97.42</v>
       </c>
       <c r="F61" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="G61">
         <v>105637.59</v>
       </c>
       <c r="I61" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="62" spans="1:9">
-      <c r="A62" t="s">
-        <v>22</v>
+        <v>49</v>
+      </c>
+      <c r="J61" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10">
+      <c r="A62">
+        <v>1481</v>
       </c>
       <c r="B62" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="C62" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="D62" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="E62">
         <v>38520.36</v>
       </c>
       <c r="F62" t="s">
-        <v>58</v>
+        <v>39</v>
       </c>
       <c r="G62">
         <v>105637.59</v>
       </c>
       <c r="I62" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="63" spans="1:9">
-      <c r="A63" t="s">
-        <v>22</v>
+        <v>49</v>
+      </c>
+      <c r="J62" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10">
+      <c r="A63">
+        <v>1481</v>
       </c>
       <c r="B63" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="C63" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="D63" t="s">
-        <v>58</v>
+        <v>39</v>
       </c>
       <c r="E63">
         <v>38520.36</v>
       </c>
       <c r="F63" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="G63">
         <v>105637.59</v>
       </c>
       <c r="I63" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="64" spans="1:9">
-      <c r="A64" t="s">
-        <v>22</v>
+        <v>49</v>
+      </c>
+      <c r="J63" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10">
+      <c r="A64">
+        <v>1481</v>
       </c>
       <c r="B64" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="C64" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="D64" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="E64">
         <v>34718.65</v>
       </c>
       <c r="F64" t="s">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="G64">
         <v>105637.59</v>
       </c>
       <c r="I64" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="65" spans="1:9">
-      <c r="A65" t="s">
-        <v>22</v>
+        <v>49</v>
+      </c>
+      <c r="J64" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10">
+      <c r="A65">
+        <v>1481</v>
       </c>
       <c r="B65" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="C65" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="D65" t="s">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="E65">
         <v>34718.65</v>
       </c>
       <c r="F65" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="G65">
         <v>105637.59</v>
       </c>
       <c r="I65" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="66" spans="1:9">
-      <c r="A66" t="s">
-        <v>22</v>
+        <v>49</v>
+      </c>
+      <c r="J65" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10">
+      <c r="A66">
+        <v>1481</v>
       </c>
       <c r="B66" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="C66" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="D66" t="s">
-        <v>60</v>
+        <v>41</v>
       </c>
       <c r="E66">
         <v>78461.92</v>
       </c>
       <c r="F66" t="s">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="G66">
         <v>78461.92</v>
       </c>
       <c r="I66" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="67" spans="1:9">
-      <c r="A67" t="s">
-        <v>22</v>
+        <v>49</v>
+      </c>
+      <c r="J66" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10">
+      <c r="A67">
+        <v>1481</v>
       </c>
       <c r="B67" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="C67" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="D67" t="s">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="E67">
         <v>78461.92</v>
       </c>
       <c r="F67" t="s">
-        <v>60</v>
+        <v>41</v>
       </c>
       <c r="G67">
         <v>78461.92</v>
       </c>
       <c r="I67" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="68" spans="1:9">
-      <c r="A68" t="s">
-        <v>23</v>
+        <v>49</v>
+      </c>
+      <c r="J67" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10">
+      <c r="A68">
+        <v>1486</v>
       </c>
       <c r="B68" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="C68" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="D68" t="s">
-        <v>61</v>
+        <v>42</v>
       </c>
       <c r="E68">
         <v>321.78</v>
       </c>
       <c r="F68" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="G68">
         <v>8287.23</v>
       </c>
       <c r="I68" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="69" spans="1:9">
-      <c r="A69" t="s">
-        <v>23</v>
+        <v>49</v>
+      </c>
+      <c r="J68" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10">
+      <c r="A69">
+        <v>1486</v>
       </c>
       <c r="B69" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="C69" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="D69" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="E69">
         <v>321.78</v>
       </c>
       <c r="F69" t="s">
-        <v>61</v>
+        <v>42</v>
       </c>
       <c r="G69">
         <v>8287.23</v>
       </c>
       <c r="I69" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="70" spans="1:9">
-      <c r="A70" t="s">
-        <v>23</v>
+        <v>49</v>
+      </c>
+      <c r="J69" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10">
+      <c r="A70">
+        <v>1486</v>
       </c>
       <c r="B70" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="C70" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="D70" t="s">
-        <v>61</v>
+        <v>42</v>
       </c>
       <c r="E70">
         <v>7965.45</v>
       </c>
       <c r="F70" t="s">
-        <v>62</v>
+        <v>43</v>
       </c>
       <c r="G70">
         <v>8287.23</v>
       </c>
       <c r="I70" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="71" spans="1:9">
-      <c r="A71" t="s">
-        <v>23</v>
+        <v>49</v>
+      </c>
+      <c r="J70" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10">
+      <c r="A71">
+        <v>1486</v>
       </c>
       <c r="B71" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="C71" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="D71" t="s">
-        <v>62</v>
+        <v>43</v>
       </c>
       <c r="E71">
         <v>7965.45</v>
       </c>
       <c r="F71" t="s">
-        <v>61</v>
+        <v>42</v>
       </c>
       <c r="G71">
         <v>8287.23</v>
       </c>
       <c r="I71" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="72" spans="1:9">
-      <c r="A72" t="s">
-        <v>24</v>
+        <v>49</v>
+      </c>
+      <c r="J71" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10">
+      <c r="A72">
+        <v>1490</v>
       </c>
       <c r="B72" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="C72" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="D72" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="E72">
         <v>1149.04</v>
       </c>
       <c r="F72" t="s">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="G72">
         <v>1149.04</v>
       </c>
       <c r="I72" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="73" spans="1:9">
-      <c r="A73" t="s">
-        <v>24</v>
+        <v>49</v>
+      </c>
+      <c r="J72" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10">
+      <c r="A73">
+        <v>1490</v>
       </c>
       <c r="B73" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="C73" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="D73" t="s">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="E73">
         <v>1149.04</v>
       </c>
       <c r="F73" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="G73">
         <v>1149.04</v>
       </c>
       <c r="I73" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="74" spans="1:9">
-      <c r="A74" t="s">
-        <v>25</v>
+        <v>49</v>
+      </c>
+      <c r="J73" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10">
+      <c r="A74">
+        <v>1498</v>
       </c>
       <c r="B74" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="C74" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="D74" t="s">
-        <v>63</v>
+        <v>44</v>
       </c>
       <c r="E74">
         <v>64401.82</v>
       </c>
       <c r="F74" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="G74">
         <v>64401.82</v>
       </c>
       <c r="I74" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="75" spans="1:9">
-      <c r="A75" t="s">
-        <v>25</v>
+        <v>49</v>
+      </c>
+      <c r="J74" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10">
+      <c r="A75">
+        <v>1498</v>
       </c>
       <c r="B75" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="C75" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="D75" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="E75">
         <v>64401.82</v>
       </c>
       <c r="F75" t="s">
-        <v>63</v>
+        <v>44</v>
       </c>
       <c r="G75">
         <v>64401.82</v>
       </c>
       <c r="I75" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="76" spans="1:9">
-      <c r="A76" t="s">
-        <v>25</v>
+        <v>49</v>
+      </c>
+      <c r="J75" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10">
+      <c r="A76">
+        <v>1498</v>
       </c>
       <c r="B76" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="C76" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="D76" t="s">
-        <v>64</v>
+        <v>45</v>
       </c>
       <c r="E76">
         <v>160118.05</v>
       </c>
       <c r="F76" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="G76">
         <v>160118.05</v>
       </c>
       <c r="I76" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="77" spans="1:9">
-      <c r="A77" t="s">
-        <v>25</v>
+        <v>49</v>
+      </c>
+      <c r="J76" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10">
+      <c r="A77">
+        <v>1498</v>
       </c>
       <c r="B77" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="C77" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="D77" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="E77">
         <v>160118.05</v>
       </c>
       <c r="F77" t="s">
-        <v>64</v>
+        <v>45</v>
       </c>
       <c r="G77">
         <v>160118.05</v>
       </c>
       <c r="I77" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="78" spans="1:9">
-      <c r="A78" t="s">
-        <v>25</v>
+        <v>49</v>
+      </c>
+      <c r="J77" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10">
+      <c r="A78">
+        <v>1498</v>
       </c>
       <c r="B78" t="s">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="C78" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="D78" t="s">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="E78">
         <v>135.08</v>
       </c>
       <c r="F78" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="G78">
         <v>135.08</v>
       </c>
       <c r="I78" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="79" spans="1:9">
-      <c r="A79" t="s">
-        <v>25</v>
+        <v>49</v>
+      </c>
+      <c r="J78" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10">
+      <c r="A79">
+        <v>1498</v>
       </c>
       <c r="B79" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="C79" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="D79" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="E79">
         <v>135.08</v>
       </c>
       <c r="F79" t="s">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="G79">
         <v>135.08</v>
       </c>
       <c r="I79" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="80" spans="1:9">
-      <c r="A80" t="s">
-        <v>26</v>
+        <v>49</v>
+      </c>
+      <c r="J79" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10">
+      <c r="A80">
+        <v>1514</v>
       </c>
       <c r="B80" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="C80" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="D80" t="s">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="E80">
         <v>2577.61</v>
       </c>
       <c r="F80" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="G80">
         <v>204151.77</v>
       </c>
       <c r="I80" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="81" spans="1:9">
-      <c r="A81" t="s">
-        <v>26</v>
+        <v>49</v>
+      </c>
+      <c r="J80" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10">
+      <c r="A81">
+        <v>1514</v>
       </c>
       <c r="B81" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="C81" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="D81" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="E81">
         <v>2577.61</v>
       </c>
       <c r="F81" t="s">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="G81">
         <v>204151.77</v>
       </c>
       <c r="I81" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="82" spans="1:9">
-      <c r="A82" t="s">
-        <v>27</v>
+        <v>49</v>
+      </c>
+      <c r="J81" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10">
+      <c r="A82">
+        <v>1515</v>
       </c>
       <c r="B82" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="C82" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="D82" t="s">
-        <v>66</v>
+        <v>47</v>
       </c>
       <c r="E82">
         <v>1703.99</v>
       </c>
       <c r="F82" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="G82">
         <v>126570.33</v>
       </c>
       <c r="I82" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="83" spans="1:9">
-      <c r="A83" t="s">
-        <v>27</v>
+        <v>49</v>
+      </c>
+      <c r="J82" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10">
+      <c r="A83">
+        <v>1515</v>
       </c>
       <c r="B83" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="C83" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="D83" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="E83">
         <v>1703.99</v>
       </c>
       <c r="F83" t="s">
-        <v>66</v>
+        <v>47</v>
       </c>
       <c r="G83">
         <v>126570.33</v>
       </c>
       <c r="I83" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="84" spans="1:9">
-      <c r="A84" t="s">
-        <v>28</v>
+        <v>49</v>
+      </c>
+      <c r="J83" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10">
+      <c r="A84">
+        <v>1516</v>
       </c>
       <c r="B84" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="C84" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="D84" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="E84">
         <v>897.88</v>
       </c>
       <c r="F84" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="G84">
         <v>897.88</v>
       </c>
       <c r="I84" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="85" spans="1:9">
-      <c r="A85" t="s">
-        <v>28</v>
+        <v>49</v>
+      </c>
+      <c r="J84" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10">
+      <c r="A85">
+        <v>1516</v>
       </c>
       <c r="B85" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="C85" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="D85" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="E85">
         <v>897.88</v>
       </c>
       <c r="F85" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="G85">
         <v>897.88</v>
       </c>
       <c r="I85" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="86" spans="1:9">
-      <c r="A86" t="s">
-        <v>28</v>
+        <v>49</v>
+      </c>
+      <c r="J85" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10">
+      <c r="A86">
+        <v>1516</v>
       </c>
       <c r="B86" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="C86" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="D86" t="s">
-        <v>67</v>
+        <v>48</v>
       </c>
       <c r="E86">
         <v>1005.5</v>
       </c>
       <c r="F86" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="G86">
         <v>1754.18</v>
       </c>
       <c r="I86" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="87" spans="1:9">
-      <c r="A87" t="s">
-        <v>28</v>
+        <v>49</v>
+      </c>
+      <c r="J86" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10">
+      <c r="A87">
+        <v>1516</v>
       </c>
       <c r="B87" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="C87" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="D87" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="E87">
         <v>1005.5</v>
       </c>
       <c r="F87" t="s">
-        <v>67</v>
+        <v>48</v>
       </c>
       <c r="G87">
         <v>1754.18</v>
       </c>
       <c r="I87" t="s">
-        <v>68</v>
+        <v>49</v>
+      </c>
+      <c r="J87" t="s">
+        <v>53</v>
       </c>
     </row>
   </sheetData>

--- a/planilha_transferencias_audesp.xlsx
+++ b/planilha_transferencias_audesp.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="526" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="526" uniqueCount="56">
   <si>
     <t>FICHA</t>
   </si>
@@ -169,21 +169,35 @@
     <t xml:space="preserve">Locator.wait_for: Timeout 10000ms exceeded.
 Call log:
   - waiting for locator("input.dx-texteditor-input[role='combobox']").first to be visible
-    23 × locator resolved to hidden &lt;input readonly type="text" tabindex="0" role="combobox" spellcheck="false" aria-expanded="false" aria-haspopup="listbox" aria-autocomplete="none" autocomplete="chrome-off" placeholder="Selecione ..." class="dx-texteditor-input" aria-owns="dx-b859372f-fc19-69ca-31c3-1bc2d4208574" aria-controls="dx-19652cef-5c23-0195-d93d-67180546bd66"/&gt;
+    23 × locator resolved to hidden &lt;input readonly type="text" tabindex="0" role="combobox" spellcheck="false" aria-expanded="false" aria-haspopup="listbox" aria-autocomplete="none" autocomplete="chrome-off" placeholder="Selecione ..." class="dx-texteditor-input" aria-owns="dx-ecc6752b-7629-ecac-bd28-7d4843ad65bf" aria-controls="dx-e77d2321-44ec-635e-8de8-c5f852d49f19"/&gt;
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Locator.wait_for: Timeout 30000ms exceeded.
+    <t xml:space="preserve">Locator.wait_for: Timeout 10000ms exceeded.
 Call log:
-  - waiting for locator("span.dx-button-text:has-text('Novo')").first to be visible
-    62 × locator resolved to hidden &lt;span class="dx-button-text"&gt;Novo&lt;/span&gt;
+  - waiting for locator("input.dx-texteditor-input[role='combobox']").first to be visible
+    23 × locator resolved to hidden &lt;input readonly type="text" tabindex="0" role="combobox" spellcheck="false" aria-expanded="false" aria-haspopup="listbox" aria-autocomplete="none" autocomplete="chrome-off" placeholder="Selecione ..." class="dx-texteditor-input" aria-owns="dx-81c13e47-5c66-aab2-bec2-cf5c7a88f1f5" aria-controls="dx-e9d4684d-9ac6-dd41-957b-ab9265144174"/&gt;
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Locator.wait_for: Timeout 10000ms exceeded.
+Call log:
+  - waiting for locator("input.dx-texteditor-input[role='combobox']").first to be visible
+    23 × locator resolved to hidden &lt;input readonly type="text" tabindex="0" role="combobox" spellcheck="false" aria-expanded="false" aria-haspopup="listbox" aria-autocomplete="none" autocomplete="chrome-off" placeholder="Selecione ..." class="dx-texteditor-input" aria-owns="dx-f182a7f3-fa63-4792-16dc-d89fa3615799" aria-controls="dx-ac29cd15-6fd7-8252-7d6b-125d1dc23512"/&gt;
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Locator.wait_for: Timeout 10000ms exceeded.
+Call log:
+  - waiting for locator("input.dx-texteditor-input[role='combobox']").first to be visible
+    23 × locator resolved to hidden &lt;input readonly type="text" tabindex="0" role="combobox" spellcheck="false" aria-expanded="false" aria-haspopup="listbox" aria-autocomplete="none" autocomplete="chrome-off" placeholder="Selecione ..." class="dx-texteditor-input" aria-owns="dx-56471b58-6a60-f71d-c0d9-1363128a3593" aria-controls="dx-66588eb8-c949-1c4d-ccae-88ce137ca18c"/&gt;
 </t>
   </si>
   <si>
     <t xml:space="preserve">Locator.wait_for: Target page, context or browser has been closed
 Call log:
-  - waiting for locator("span.dx-button-text:has-text('Novo')").first to be visible
-    56 × locator resolved to hidden &lt;span class="dx-button-text"&gt;Novo&lt;/span&gt;
+  - waiting for locator("input.dx-texteditor-input[role='combobox']").first to be visible
+    6 × locator resolved to hidden &lt;input readonly type="text" tabindex="0" role="combobox" spellcheck="false" aria-expanded="false" aria-haspopup="listbox" aria-autocomplete="none" autocomplete="chrome-off" placeholder="Selecione ..." class="dx-texteditor-input" aria-owns="dx-b7767ad1-7a89-c39f-9279-07e6aa88dc6d" aria-controls="dx-c6856b77-1769-5793-935a-c54259665a33"/&gt;
 </t>
   </si>
   <si>
@@ -1012,7 +1026,7 @@
         <v>49</v>
       </c>
       <c r="J16" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -1041,7 +1055,7 @@
         <v>49</v>
       </c>
       <c r="J17" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -1070,7 +1084,7 @@
         <v>49</v>
       </c>
       <c r="J18" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -1099,7 +1113,7 @@
         <v>49</v>
       </c>
       <c r="J19" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="20" spans="1:10">
@@ -1128,7 +1142,7 @@
         <v>49</v>
       </c>
       <c r="J20" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -1157,7 +1171,7 @@
         <v>49</v>
       </c>
       <c r="J21" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -1186,7 +1200,7 @@
         <v>49</v>
       </c>
       <c r="J22" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -1215,7 +1229,7 @@
         <v>49</v>
       </c>
       <c r="J23" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="24" spans="1:10">
@@ -1244,7 +1258,7 @@
         <v>49</v>
       </c>
       <c r="J24" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="25" spans="1:10">
@@ -1273,7 +1287,7 @@
         <v>49</v>
       </c>
       <c r="J25" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="26" spans="1:10">
@@ -1302,7 +1316,7 @@
         <v>49</v>
       </c>
       <c r="J26" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="27" spans="1:10">
@@ -1331,7 +1345,7 @@
         <v>49</v>
       </c>
       <c r="J27" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="28" spans="1:10">
@@ -1360,7 +1374,7 @@
         <v>49</v>
       </c>
       <c r="J28" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="29" spans="1:10">
@@ -1389,7 +1403,7 @@
         <v>49</v>
       </c>
       <c r="J29" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="30" spans="1:10">
@@ -1418,7 +1432,7 @@
         <v>49</v>
       </c>
       <c r="J30" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="31" spans="1:10">
@@ -1447,7 +1461,7 @@
         <v>49</v>
       </c>
       <c r="J31" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="32" spans="1:10">
@@ -1476,7 +1490,7 @@
         <v>49</v>
       </c>
       <c r="J32" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="33" spans="1:10">
@@ -1505,7 +1519,7 @@
         <v>49</v>
       </c>
       <c r="J33" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="34" spans="1:10">
@@ -1534,7 +1548,7 @@
         <v>49</v>
       </c>
       <c r="J34" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="35" spans="1:10">
@@ -1563,7 +1577,7 @@
         <v>49</v>
       </c>
       <c r="J35" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="36" spans="1:10">
@@ -1592,7 +1606,7 @@
         <v>49</v>
       </c>
       <c r="J36" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="37" spans="1:10">
@@ -1621,7 +1635,7 @@
         <v>49</v>
       </c>
       <c r="J37" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="38" spans="1:10">
@@ -1650,7 +1664,7 @@
         <v>49</v>
       </c>
       <c r="J38" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="39" spans="1:10">
@@ -1679,7 +1693,7 @@
         <v>49</v>
       </c>
       <c r="J39" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="40" spans="1:10">
@@ -1708,7 +1722,7 @@
         <v>49</v>
       </c>
       <c r="J40" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="41" spans="1:10">
@@ -1737,7 +1751,7 @@
         <v>49</v>
       </c>
       <c r="J41" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="42" spans="1:10">
@@ -1766,7 +1780,7 @@
         <v>49</v>
       </c>
       <c r="J42" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="43" spans="1:10">
@@ -1795,7 +1809,7 @@
         <v>49</v>
       </c>
       <c r="J43" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="44" spans="1:10">
@@ -1824,7 +1838,7 @@
         <v>49</v>
       </c>
       <c r="J44" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="45" spans="1:10">
@@ -1853,7 +1867,7 @@
         <v>49</v>
       </c>
       <c r="J45" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="46" spans="1:10">
@@ -1882,7 +1896,7 @@
         <v>49</v>
       </c>
       <c r="J46" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="47" spans="1:10">
@@ -1911,7 +1925,7 @@
         <v>49</v>
       </c>
       <c r="J47" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="48" spans="1:10">
@@ -1940,7 +1954,7 @@
         <v>49</v>
       </c>
       <c r="J48" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="49" spans="1:10">
@@ -1969,7 +1983,7 @@
         <v>49</v>
       </c>
       <c r="J49" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="50" spans="1:10">
@@ -1998,7 +2012,7 @@
         <v>49</v>
       </c>
       <c r="J50" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="51" spans="1:10">
@@ -2027,7 +2041,7 @@
         <v>49</v>
       </c>
       <c r="J51" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="52" spans="1:10">
@@ -2056,7 +2070,7 @@
         <v>49</v>
       </c>
       <c r="J52" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="53" spans="1:10">
@@ -2085,7 +2099,7 @@
         <v>49</v>
       </c>
       <c r="J53" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="54" spans="1:10">
@@ -2114,7 +2128,7 @@
         <v>49</v>
       </c>
       <c r="J54" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="55" spans="1:10">
@@ -2143,7 +2157,7 @@
         <v>49</v>
       </c>
       <c r="J55" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="56" spans="1:10">
@@ -2172,7 +2186,7 @@
         <v>49</v>
       </c>
       <c r="J56" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="57" spans="1:10">
@@ -2201,7 +2215,7 @@
         <v>49</v>
       </c>
       <c r="J57" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="58" spans="1:10">
@@ -2230,7 +2244,7 @@
         <v>49</v>
       </c>
       <c r="J58" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="59" spans="1:10">
@@ -2259,7 +2273,7 @@
         <v>49</v>
       </c>
       <c r="J59" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="60" spans="1:10">
@@ -2288,7 +2302,7 @@
         <v>49</v>
       </c>
       <c r="J60" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="61" spans="1:10">
@@ -2317,7 +2331,7 @@
         <v>49</v>
       </c>
       <c r="J61" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="62" spans="1:10">
@@ -2346,7 +2360,7 @@
         <v>49</v>
       </c>
       <c r="J62" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="63" spans="1:10">
@@ -2375,7 +2389,7 @@
         <v>49</v>
       </c>
       <c r="J63" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="64" spans="1:10">
@@ -2404,7 +2418,7 @@
         <v>49</v>
       </c>
       <c r="J64" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="65" spans="1:10">
@@ -2433,7 +2447,7 @@
         <v>49</v>
       </c>
       <c r="J65" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="66" spans="1:10">
@@ -2462,7 +2476,7 @@
         <v>49</v>
       </c>
       <c r="J66" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="67" spans="1:10">
@@ -2491,7 +2505,7 @@
         <v>49</v>
       </c>
       <c r="J67" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="68" spans="1:10">
@@ -2520,7 +2534,7 @@
         <v>49</v>
       </c>
       <c r="J68" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="69" spans="1:10">
@@ -2549,7 +2563,7 @@
         <v>49</v>
       </c>
       <c r="J69" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="70" spans="1:10">
@@ -2578,7 +2592,7 @@
         <v>49</v>
       </c>
       <c r="J70" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="71" spans="1:10">
@@ -2607,7 +2621,7 @@
         <v>49</v>
       </c>
       <c r="J71" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="72" spans="1:10">
@@ -2636,7 +2650,7 @@
         <v>49</v>
       </c>
       <c r="J72" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="73" spans="1:10">
@@ -2665,7 +2679,7 @@
         <v>49</v>
       </c>
       <c r="J73" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="74" spans="1:10">
@@ -2694,7 +2708,7 @@
         <v>49</v>
       </c>
       <c r="J74" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="75" spans="1:10">
@@ -2723,7 +2737,7 @@
         <v>49</v>
       </c>
       <c r="J75" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="76" spans="1:10">
@@ -2752,7 +2766,7 @@
         <v>49</v>
       </c>
       <c r="J76" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="77" spans="1:10">
@@ -2781,7 +2795,7 @@
         <v>49</v>
       </c>
       <c r="J77" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="78" spans="1:10">
@@ -2810,7 +2824,7 @@
         <v>49</v>
       </c>
       <c r="J78" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="79" spans="1:10">
@@ -2839,7 +2853,7 @@
         <v>49</v>
       </c>
       <c r="J79" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="80" spans="1:10">
@@ -2868,7 +2882,7 @@
         <v>49</v>
       </c>
       <c r="J80" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="81" spans="1:10">
@@ -2897,7 +2911,7 @@
         <v>49</v>
       </c>
       <c r="J81" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="82" spans="1:10">
@@ -2926,7 +2940,7 @@
         <v>49</v>
       </c>
       <c r="J82" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="83" spans="1:10">
@@ -2955,7 +2969,7 @@
         <v>49</v>
       </c>
       <c r="J83" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="84" spans="1:10">
@@ -2984,7 +2998,7 @@
         <v>49</v>
       </c>
       <c r="J84" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="85" spans="1:10">
@@ -3013,7 +3027,7 @@
         <v>49</v>
       </c>
       <c r="J85" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="86" spans="1:10">
@@ -3042,7 +3056,7 @@
         <v>49</v>
       </c>
       <c r="J86" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="87" spans="1:10">
@@ -3071,7 +3085,7 @@
         <v>49</v>
       </c>
       <c r="J87" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
   </sheetData>
